--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3908" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="10337" uniqueCount="526">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="10337" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="12480" uniqueCount="526">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="12480" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="18774" uniqueCount="559">
   <si>
     <t>Year</t>
   </si>
@@ -1592,6 +1592,105 @@
   </si>
   <si>
     <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch2\wednesday\wednesday_111518\fracture\Fracture_20231115_185304_3_2.csv</t>
+  </si>
+  <si>
+    <t>wednesday_040508</t>
+  </si>
+  <si>
+    <t>wednesday_040514</t>
+  </si>
+  <si>
+    <t>wednesday_040517</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\compression\COMPRESSION_20230405_91656_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\compression\COMPRESSION_20230405_91423_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\tension\TENSION_20230405_90545_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\tension\TENSION_20230405_90913_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\fracture\Fracture_20230405_85157_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\fracture\Fracture_20230405_85748_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\fracture\Fracture_20230405_85748_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\fracture\Fracture_20230405_85157_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\fracture\Fracture_20230405_85157_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\fracture\Fracture_20230405_85157_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\fracture\Fracture_20230405_85748_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040508\fracture\Fracture_20230405_85748_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040514\tension\TENSION_20230405_140132_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040514\tension\TENSION_20230405_140132_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040514\fracture\Fracture_20230405_142401_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040514\fracture\Fracture_20230405_142401_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040514\fracture\Fracture_20230405_142401_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040514\fracture\Fracture_20230403_92519_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\compression\COMPRESSION_20230405_171714_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\compression\COMPRESSION_20230405_171714_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\tension\TENSION_20230405_173912_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\tension\TENSION_20230405_173912_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_164927_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_164927_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_164927_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_170828_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_170828_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_164927_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_170828_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\batch1\wednesday\wednesday_040517\fracture\Fracture_20230405_170828_3_2.csv</t>
   </si>
 </sst>
 </file>
@@ -4191,7 +4290,7 @@
         <v>438</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>439</v>
+        <v>526</v>
       </c>
       <c r="E80" s="0" t="s">
         <v>30</v>
@@ -4206,7 +4305,7 @@
         <v>443</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>484</v>
+        <v>529</v>
       </c>
       <c r="J80" s="0">
         <v>10499.483399999999</v>
@@ -4223,7 +4322,7 @@
         <v>438</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>439</v>
+        <v>526</v>
       </c>
       <c r="E81" s="0" t="s">
         <v>30</v>
@@ -4238,7 +4337,7 @@
         <v>444</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>485</v>
+        <v>530</v>
       </c>
       <c r="J81" s="0">
         <v>9639.3300999999992</v>
@@ -4255,7 +4354,7 @@
         <v>438</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>439</v>
+        <v>526</v>
       </c>
       <c r="E82" s="0" t="s">
         <v>31</v>
@@ -4270,7 +4369,7 @@
         <v>445</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>486</v>
+        <v>531</v>
       </c>
       <c r="J82" s="0">
         <v>1567.0791999999999</v>
@@ -4287,7 +4386,7 @@
         <v>438</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>439</v>
+        <v>526</v>
       </c>
       <c r="E83" s="0" t="s">
         <v>31</v>
@@ -4302,7 +4401,7 @@
         <v>446</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>487</v>
+        <v>532</v>
       </c>
       <c r="J83" s="0">
         <v>1003.1186</v>
@@ -4319,7 +4418,7 @@
         <v>438</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>439</v>
+        <v>526</v>
       </c>
       <c r="E84" s="0" t="s">
         <v>32</v>
@@ -4334,7 +4433,7 @@
         <v>447</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>488</v>
+        <v>533</v>
       </c>
       <c r="J84" s="0">
         <v>388.74549999999999</v>
@@ -4351,7 +4450,7 @@
         <v>438</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>439</v>
+        <v>526</v>
       </c>
       <c r="E85" s="0" t="s">
         <v>32</v>
@@ -4366,7 +4465,7 @@
         <v>448</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>489</v>
+        <v>534</v>
       </c>
       <c r="J85" s="0">
         <v>308.16899999999998</v>
@@ -4383,7 +4482,7 @@
         <v>438</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>439</v>
+        <v>526</v>
       </c>
       <c r="E86" s="0" t="s">
         <v>32</v>
@@ -4398,7 +4497,7 @@
         <v>449</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>490</v>
+        <v>535</v>
       </c>
       <c r="J86" s="0">
         <v>305.76100000000002</v>
@@ -4415,7 +4514,7 @@
         <v>438</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>439</v>
+        <v>526</v>
       </c>
       <c r="E87" s="0" t="s">
         <v>32</v>
@@ -4430,7 +4529,7 @@
         <v>450</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>491</v>
+        <v>536</v>
       </c>
       <c r="J87" s="0">
         <v>304.48329999999999</v>
@@ -4447,7 +4546,7 @@
         <v>438</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>439</v>
+        <v>526</v>
       </c>
       <c r="E88" s="0" t="s">
         <v>32</v>
@@ -4462,7 +4561,7 @@
         <v>451</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>492</v>
+        <v>537</v>
       </c>
       <c r="J88" s="0">
         <v>297.43759999999998</v>
@@ -4479,7 +4578,7 @@
         <v>438</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>439</v>
+        <v>526</v>
       </c>
       <c r="E89" s="0" t="s">
         <v>32</v>
@@ -4494,7 +4593,7 @@
         <v>452</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>493</v>
+        <v>538</v>
       </c>
       <c r="J89" s="0">
         <v>283.1619</v>
@@ -4511,7 +4610,7 @@
         <v>438</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>439</v>
+        <v>526</v>
       </c>
       <c r="E90" s="0" t="s">
         <v>32</v>
@@ -4526,7 +4625,7 @@
         <v>453</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>494</v>
+        <v>539</v>
       </c>
       <c r="J90" s="0">
         <v>247.529</v>
@@ -4543,7 +4642,7 @@
         <v>438</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>439</v>
+        <v>526</v>
       </c>
       <c r="E91" s="0" t="s">
         <v>32</v>
@@ -4558,7 +4657,7 @@
         <v>454</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>495</v>
+        <v>540</v>
       </c>
       <c r="J91" s="0">
         <v>231.5712</v>
@@ -4575,7 +4674,7 @@
         <v>438</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>440</v>
+        <v>527</v>
       </c>
       <c r="E92" s="0" t="s">
         <v>31</v>
@@ -4590,7 +4689,7 @@
         <v>455</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>496</v>
+        <v>541</v>
       </c>
       <c r="J92" s="0">
         <v>1517.5046</v>
@@ -4607,7 +4706,7 @@
         <v>438</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>440</v>
+        <v>527</v>
       </c>
       <c r="E93" s="0" t="s">
         <v>31</v>
@@ -4622,7 +4721,7 @@
         <v>456</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>497</v>
+        <v>542</v>
       </c>
       <c r="J93" s="0">
         <v>1414.645</v>
@@ -4639,7 +4738,7 @@
         <v>438</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>440</v>
+        <v>527</v>
       </c>
       <c r="E94" s="0" t="s">
         <v>32</v>
@@ -4654,7 +4753,7 @@
         <v>457</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>498</v>
+        <v>543</v>
       </c>
       <c r="J94" s="0">
         <v>385.28089999999998</v>
@@ -4671,7 +4770,7 @@
         <v>438</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>440</v>
+        <v>527</v>
       </c>
       <c r="E95" s="0" t="s">
         <v>32</v>
@@ -4686,7 +4785,7 @@
         <v>458</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>499</v>
+        <v>544</v>
       </c>
       <c r="J95" s="0">
         <v>310.61110000000002</v>
@@ -4703,7 +4802,7 @@
         <v>438</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>440</v>
+        <v>527</v>
       </c>
       <c r="E96" s="0" t="s">
         <v>32</v>
@@ -4718,7 +4817,7 @@
         <v>459</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>500</v>
+        <v>545</v>
       </c>
       <c r="J96" s="0">
         <v>277.84199999999999</v>
@@ -4735,7 +4834,7 @@
         <v>438</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>440</v>
+        <v>527</v>
       </c>
       <c r="E97" s="0" t="s">
         <v>32</v>
@@ -4750,7 +4849,7 @@
         <v>63</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>501</v>
+        <v>546</v>
       </c>
       <c r="J97" s="0">
         <v>223.45169999999999</v>
@@ -4767,7 +4866,7 @@
         <v>438</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>441</v>
+        <v>528</v>
       </c>
       <c r="E98" s="0" t="s">
         <v>30</v>
@@ -4782,7 +4881,7 @@
         <v>460</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>502</v>
+        <v>547</v>
       </c>
       <c r="J98" s="0">
         <v>10215.762699999999</v>
@@ -4799,7 +4898,7 @@
         <v>438</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>441</v>
+        <v>528</v>
       </c>
       <c r="E99" s="0" t="s">
         <v>30</v>
@@ -4814,7 +4913,7 @@
         <v>461</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>503</v>
+        <v>548</v>
       </c>
       <c r="J99" s="0">
         <v>8851.0136999999995</v>
@@ -4831,7 +4930,7 @@
         <v>438</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>441</v>
+        <v>528</v>
       </c>
       <c r="E100" s="0" t="s">
         <v>31</v>
@@ -4846,7 +4945,7 @@
         <v>462</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>504</v>
+        <v>549</v>
       </c>
       <c r="J100" s="0">
         <v>1106.4232</v>
@@ -4863,7 +4962,7 @@
         <v>438</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>441</v>
+        <v>528</v>
       </c>
       <c r="E101" s="0" t="s">
         <v>31</v>
@@ -4878,7 +4977,7 @@
         <v>463</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>505</v>
+        <v>550</v>
       </c>
       <c r="J101" s="0">
         <v>909.94200000000001</v>
@@ -4895,7 +4994,7 @@
         <v>438</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>441</v>
+        <v>528</v>
       </c>
       <c r="E102" s="0" t="s">
         <v>32</v>
@@ -4910,7 +5009,7 @@
         <v>464</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>506</v>
+        <v>551</v>
       </c>
       <c r="J102" s="0">
         <v>316.77910000000003</v>
@@ -4927,7 +5026,7 @@
         <v>438</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>441</v>
+        <v>528</v>
       </c>
       <c r="E103" s="0" t="s">
         <v>32</v>
@@ -4942,7 +5041,7 @@
         <v>465</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>507</v>
+        <v>552</v>
       </c>
       <c r="J103" s="0">
         <v>284.43700000000001</v>
@@ -4959,7 +5058,7 @@
         <v>438</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>441</v>
+        <v>528</v>
       </c>
       <c r="E104" s="0" t="s">
         <v>32</v>
@@ -4974,7 +5073,7 @@
         <v>466</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>508</v>
+        <v>553</v>
       </c>
       <c r="J104" s="0">
         <v>282.07659999999999</v>
@@ -4991,7 +5090,7 @@
         <v>438</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>441</v>
+        <v>528</v>
       </c>
       <c r="E105" s="0" t="s">
         <v>32</v>
@@ -5006,7 +5105,7 @@
         <v>467</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>509</v>
+        <v>554</v>
       </c>
       <c r="J105" s="0">
         <v>261.52760000000001</v>
@@ -5023,7 +5122,7 @@
         <v>438</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>441</v>
+        <v>528</v>
       </c>
       <c r="E106" s="0" t="s">
         <v>32</v>
@@ -5038,7 +5137,7 @@
         <v>468</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>510</v>
+        <v>555</v>
       </c>
       <c r="J106" s="0">
         <v>248.01570000000001</v>
@@ -5055,7 +5154,7 @@
         <v>438</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>441</v>
+        <v>528</v>
       </c>
       <c r="E107" s="0" t="s">
         <v>32</v>
@@ -5070,7 +5169,7 @@
         <v>469</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>511</v>
+        <v>556</v>
       </c>
       <c r="J107" s="0">
         <v>246.53380000000001</v>
@@ -5087,7 +5186,7 @@
         <v>438</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>441</v>
+        <v>528</v>
       </c>
       <c r="E108" s="0" t="s">
         <v>32</v>
@@ -5102,7 +5201,7 @@
         <v>470</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>512</v>
+        <v>557</v>
       </c>
       <c r="J108" s="0">
         <v>228.9768</v>
@@ -5119,7 +5218,7 @@
         <v>438</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>441</v>
+        <v>528</v>
       </c>
       <c r="E109" s="0" t="s">
         <v>32</v>
@@ -5134,7 +5233,7 @@
         <v>471</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>513</v>
+        <v>558</v>
       </c>
       <c r="J109" s="0">
         <v>216.21680000000001</v>
@@ -6242,22 +6341,22 @@
         <v>22</v>
       </c>
       <c r="E144" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G144" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J144" s="0">
-        <v>6732.1445000000003</v>
+        <v>908.87840000000006</v>
       </c>
     </row>
     <row r="145">
@@ -6277,19 +6376,19 @@
         <v>31</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G145" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J145" s="0">
-        <v>908.87840000000006</v>
+        <v>840.46699999999999</v>
       </c>
     </row>
     <row r="146">
@@ -6306,22 +6405,22 @@
         <v>22</v>
       </c>
       <c r="E146" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J146" s="0">
-        <v>840.46699999999999</v>
+        <v>385.22919999999999</v>
       </c>
     </row>
     <row r="147">
@@ -6341,19 +6440,19 @@
         <v>32</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J147" s="0">
-        <v>385.22919999999999</v>
+        <v>310.47890000000001</v>
       </c>
     </row>
     <row r="148">
@@ -6373,19 +6472,19 @@
         <v>32</v>
       </c>
       <c r="F148" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G148" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J148" s="0">
-        <v>310.47890000000001</v>
+        <v>300.91699999999997</v>
       </c>
     </row>
     <row r="149">
@@ -6405,19 +6504,19 @@
         <v>32</v>
       </c>
       <c r="F149" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G149" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J149" s="0">
-        <v>300.91699999999997</v>
+        <v>285.7113</v>
       </c>
     </row>
     <row r="150">
@@ -6437,19 +6536,19 @@
         <v>32</v>
       </c>
       <c r="F150" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G150" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J150" s="0">
-        <v>285.7113</v>
+        <v>255.1182</v>
       </c>
     </row>
     <row r="151">
@@ -6469,19 +6568,19 @@
         <v>32</v>
       </c>
       <c r="F151" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G151" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J151" s="0">
-        <v>255.1182</v>
+        <v>251.63229999999999</v>
       </c>
     </row>
     <row r="152">
@@ -6501,19 +6600,19 @@
         <v>32</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G152" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J152" s="0">
-        <v>251.63229999999999</v>
+        <v>241.47989999999999</v>
       </c>
     </row>
     <row r="153">
@@ -6533,19 +6632,19 @@
         <v>32</v>
       </c>
       <c r="F153" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G153" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H153" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J153" s="0">
-        <v>241.47989999999999</v>
+        <v>239.88820000000001</v>
       </c>
     </row>
     <row r="154">
@@ -6556,28 +6655,28 @@
         <v>3</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D154" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E154" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F154" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G154" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J154" s="0">
-        <v>239.88820000000001</v>
+        <v>10661.891600000001</v>
       </c>
     </row>
     <row r="155">
@@ -6597,19 +6696,19 @@
         <v>30</v>
       </c>
       <c r="F155" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G155" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J155" s="0">
-        <v>10661.891600000001</v>
+        <v>7643.7520000000004</v>
       </c>
     </row>
     <row r="156">
@@ -6626,22 +6725,22 @@
         <v>23</v>
       </c>
       <c r="E156" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F156" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G156" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J156" s="0">
-        <v>7643.7520000000004</v>
+        <v>1539.2754</v>
       </c>
     </row>
     <row r="157">
@@ -6661,19 +6760,19 @@
         <v>31</v>
       </c>
       <c r="F157" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G157" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H157" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J157" s="0">
-        <v>1539.2754</v>
+        <v>1393.9193</v>
       </c>
     </row>
     <row r="158">
@@ -6690,22 +6789,22 @@
         <v>23</v>
       </c>
       <c r="E158" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F158" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H158" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J158" s="0">
-        <v>1393.9193</v>
+        <v>457.66739999999999</v>
       </c>
     </row>
     <row r="159">
@@ -6725,19 +6824,19 @@
         <v>32</v>
       </c>
       <c r="F159" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G159" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H159" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J159" s="0">
-        <v>457.66739999999999</v>
+        <v>419.16669999999999</v>
       </c>
     </row>
     <row r="160">
@@ -6757,19 +6856,19 @@
         <v>32</v>
       </c>
       <c r="F160" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G160" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H160" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J160" s="0">
-        <v>419.16669999999999</v>
+        <v>417.49169999999998</v>
       </c>
     </row>
     <row r="161">
@@ -6789,19 +6888,19 @@
         <v>32</v>
       </c>
       <c r="F161" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G161" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H161" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J161" s="0">
-        <v>417.49169999999998</v>
+        <v>399.00799999999998</v>
       </c>
     </row>
     <row r="162">
@@ -6821,19 +6920,19 @@
         <v>32</v>
       </c>
       <c r="F162" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G162" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H162" s="0" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J162" s="0">
-        <v>399.00799999999998</v>
+        <v>361.1662</v>
       </c>
     </row>
     <row r="163">
@@ -6853,19 +6952,19 @@
         <v>32</v>
       </c>
       <c r="F163" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G163" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H163" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J163" s="0">
-        <v>361.1662</v>
+        <v>329.83010000000002</v>
       </c>
     </row>
     <row r="164">
@@ -6885,19 +6984,19 @@
         <v>32</v>
       </c>
       <c r="F164" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G164" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H164" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J164" s="0">
-        <v>329.83010000000002</v>
+        <v>311.19600000000003</v>
       </c>
     </row>
     <row r="165">
@@ -6917,19 +7016,19 @@
         <v>32</v>
       </c>
       <c r="F165" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G165" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H165" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J165" s="0">
-        <v>311.19600000000003</v>
+        <v>291.23480000000001</v>
       </c>
     </row>
     <row r="166">
@@ -6943,25 +7042,25 @@
         <v>8</v>
       </c>
       <c r="D166" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E166" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F166" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G166" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J166" s="0">
-        <v>291.23480000000001</v>
+        <v>9127.5985999999994</v>
       </c>
     </row>
     <row r="167">
@@ -6981,19 +7080,19 @@
         <v>30</v>
       </c>
       <c r="F167" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G167" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J167" s="0">
-        <v>9127.5985999999994</v>
+        <v>8554.8642999999993</v>
       </c>
     </row>
     <row r="168">
@@ -7010,22 +7109,22 @@
         <v>24</v>
       </c>
       <c r="E168" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F168" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G168" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J168" s="0">
-        <v>8554.8642999999993</v>
+        <v>1414.848</v>
       </c>
     </row>
     <row r="169">
@@ -7045,19 +7144,19 @@
         <v>31</v>
       </c>
       <c r="F169" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G169" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H169" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J169" s="0">
-        <v>1414.848</v>
+        <v>752.67660000000001</v>
       </c>
     </row>
     <row r="170">
@@ -7074,22 +7173,22 @@
         <v>24</v>
       </c>
       <c r="E170" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F170" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G170" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H170" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J170" s="0">
-        <v>752.67660000000001</v>
+        <v>348.73090000000002</v>
       </c>
     </row>
     <row r="171">
@@ -7109,19 +7208,19 @@
         <v>32</v>
       </c>
       <c r="F171" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G171" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H171" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J171" s="0">
-        <v>348.73090000000002</v>
+        <v>307.04939999999999</v>
       </c>
     </row>
     <row r="172">
@@ -7141,19 +7240,19 @@
         <v>32</v>
       </c>
       <c r="F172" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G172" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H172" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J172" s="0">
-        <v>307.04939999999999</v>
+        <v>280.97919999999999</v>
       </c>
     </row>
     <row r="173">
@@ -7173,19 +7272,19 @@
         <v>32</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G173" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J173" s="0">
-        <v>280.97919999999999</v>
+        <v>265.1284</v>
       </c>
     </row>
     <row r="174">
@@ -7205,19 +7304,19 @@
         <v>32</v>
       </c>
       <c r="F174" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G174" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J174" s="0">
-        <v>265.1284</v>
+        <v>249.8895</v>
       </c>
     </row>
     <row r="175">
@@ -7237,19 +7336,19 @@
         <v>32</v>
       </c>
       <c r="F175" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G175" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J175" s="0">
-        <v>249.8895</v>
+        <v>215.3955</v>
       </c>
     </row>
     <row r="176">
@@ -7269,19 +7368,19 @@
         <v>32</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G176" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J176" s="0">
-        <v>215.3955</v>
+        <v>213.6302</v>
       </c>
     </row>
     <row r="177">
@@ -7301,19 +7400,19 @@
         <v>32</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G177" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J177" s="0">
-        <v>213.6302</v>
+        <v>193.54920000000001</v>
       </c>
     </row>
     <row r="178">
@@ -7327,25 +7426,25 @@
         <v>8</v>
       </c>
       <c r="D178" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E178" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F178" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G178" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J178" s="0">
-        <v>193.54920000000001</v>
+        <v>9254.9814000000006</v>
       </c>
     </row>
     <row r="179">
@@ -7365,19 +7464,19 @@
         <v>30</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G179" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J179" s="0">
-        <v>9254.9814000000006</v>
+        <v>8396.3974999999991</v>
       </c>
     </row>
     <row r="180">
@@ -7394,22 +7493,22 @@
         <v>25</v>
       </c>
       <c r="E180" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F180" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G180" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J180" s="0">
-        <v>8396.3974999999991</v>
+        <v>1087.1931999999999</v>
       </c>
     </row>
     <row r="181">
@@ -7429,19 +7528,19 @@
         <v>31</v>
       </c>
       <c r="F181" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G181" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J181" s="0">
-        <v>1087.1931999999999</v>
+        <v>1026.0048999999999</v>
       </c>
     </row>
     <row r="182">
@@ -7458,22 +7557,22 @@
         <v>25</v>
       </c>
       <c r="E182" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F182" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G182" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H182" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J182" s="0">
-        <v>1026.0048999999999</v>
+        <v>328.2697</v>
       </c>
     </row>
     <row r="183">
@@ -7493,19 +7592,19 @@
         <v>32</v>
       </c>
       <c r="F183" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G183" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J183" s="0">
-        <v>328.2697</v>
+        <v>306.13749999999999</v>
       </c>
     </row>
     <row r="184">
@@ -7525,19 +7624,19 @@
         <v>32</v>
       </c>
       <c r="F184" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G184" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J184" s="0">
-        <v>306.13749999999999</v>
+        <v>302.69369999999998</v>
       </c>
     </row>
     <row r="185">
@@ -7557,19 +7656,19 @@
         <v>32</v>
       </c>
       <c r="F185" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G185" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J185" s="0">
-        <v>302.69369999999998</v>
+        <v>296.63529999999997</v>
       </c>
     </row>
     <row r="186">
@@ -7589,19 +7688,19 @@
         <v>32</v>
       </c>
       <c r="F186" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G186" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H186" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J186" s="0">
-        <v>296.63529999999997</v>
+        <v>292.96969999999999</v>
       </c>
     </row>
     <row r="187">
@@ -7621,19 +7720,19 @@
         <v>32</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G187" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H187" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J187" s="0">
-        <v>292.96969999999999</v>
+        <v>267.35629999999998</v>
       </c>
     </row>
     <row r="188">
@@ -7653,19 +7752,19 @@
         <v>32</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J188" s="0">
-        <v>267.35629999999998</v>
+        <v>165.21969999999999</v>
       </c>
     </row>
     <row r="189">
@@ -7679,25 +7778,25 @@
         <v>8</v>
       </c>
       <c r="D189" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E189" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F189" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G189" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H189" s="0" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="J189" s="0">
-        <v>233.2096</v>
+        <v>1713.3430000000001</v>
       </c>
     </row>
     <row r="190">
@@ -7711,25 +7810,25 @@
         <v>8</v>
       </c>
       <c r="D190" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E190" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F190" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G190" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="J190" s="0">
-        <v>165.21969999999999</v>
+        <v>1254.9603</v>
       </c>
     </row>
     <row r="191">
@@ -7746,7 +7845,7 @@
         <v>26</v>
       </c>
       <c r="E191" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F191" s="0" t="s">
         <v>34</v>
@@ -7755,13 +7854,13 @@
         <v>43</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="J191" s="0">
-        <v>12605.4648</v>
+        <v>412.1336</v>
       </c>
     </row>
     <row r="192">
@@ -7778,22 +7877,22 @@
         <v>26</v>
       </c>
       <c r="E192" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F192" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G192" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="J192" s="0">
-        <v>8687.9521000000004</v>
+        <v>395.3304</v>
       </c>
     </row>
     <row r="193">
@@ -7810,22 +7909,22 @@
         <v>26</v>
       </c>
       <c r="E193" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F193" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G193" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="J193" s="0">
-        <v>1713.3430000000001</v>
+        <v>314.40159999999997</v>
       </c>
     </row>
     <row r="194">
@@ -7842,22 +7941,22 @@
         <v>26</v>
       </c>
       <c r="E194" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F194" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G194" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="J194" s="0">
-        <v>1254.9603</v>
+        <v>306.70960000000002</v>
       </c>
     </row>
     <row r="195">
@@ -7877,19 +7976,19 @@
         <v>32</v>
       </c>
       <c r="F195" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G195" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="J195" s="0">
-        <v>412.1336</v>
+        <v>285.86070000000001</v>
       </c>
     </row>
     <row r="196">
@@ -7909,19 +8008,19 @@
         <v>32</v>
       </c>
       <c r="F196" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G196" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="J196" s="0">
-        <v>395.3304</v>
+        <v>284.4486</v>
       </c>
     </row>
     <row r="197">
@@ -7941,19 +8040,19 @@
         <v>32</v>
       </c>
       <c r="F197" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G197" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="J197" s="0">
-        <v>314.40159999999997</v>
+        <v>281.97449999999998</v>
       </c>
     </row>
     <row r="198">
@@ -7967,25 +8066,25 @@
         <v>8</v>
       </c>
       <c r="D198" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E198" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G198" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="J198" s="0">
-        <v>306.70960000000002</v>
+        <v>9423.6895000000004</v>
       </c>
     </row>
     <row r="199">
@@ -7999,10 +8098,10 @@
         <v>8</v>
       </c>
       <c r="D199" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E199" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F199" s="0" t="s">
         <v>35</v>
@@ -8011,13 +8110,13 @@
         <v>44</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="J199" s="0">
-        <v>285.86070000000001</v>
+        <v>9234.3525000000009</v>
       </c>
     </row>
     <row r="200">
@@ -8031,25 +8130,25 @@
         <v>8</v>
       </c>
       <c r="D200" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E200" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F200" s="0" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G200" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J200" s="0">
-        <v>284.4486</v>
+        <v>1208.9946</v>
       </c>
     </row>
     <row r="201">
@@ -8063,25 +8162,25 @@
         <v>8</v>
       </c>
       <c r="D201" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E201" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G201" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="J201" s="0">
-        <v>281.97449999999998</v>
+        <v>951.19749999999999</v>
       </c>
     </row>
     <row r="202">
@@ -8095,25 +8194,25 @@
         <v>8</v>
       </c>
       <c r="D202" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E202" s="0" t="s">
         <v>32</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G202" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="J202" s="0">
-        <v>273.54880000000003</v>
+        <v>316.12619999999998</v>
       </c>
     </row>
     <row r="203">
@@ -8130,22 +8229,22 @@
         <v>27</v>
       </c>
       <c r="E203" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="J203" s="0">
-        <v>9423.6895000000004</v>
+        <v>302.2124</v>
       </c>
     </row>
     <row r="204">
@@ -8162,22 +8261,22 @@
         <v>27</v>
       </c>
       <c r="E204" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F204" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G204" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="J204" s="0">
-        <v>9234.3525000000009</v>
+        <v>294.96859999999998</v>
       </c>
     </row>
     <row r="205">
@@ -8194,22 +8293,22 @@
         <v>27</v>
       </c>
       <c r="E205" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="J205" s="0">
-        <v>1208.9946</v>
+        <v>291.27109999999999</v>
       </c>
     </row>
     <row r="206">
@@ -8226,7 +8325,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F206" s="0" t="s">
         <v>35</v>
@@ -8235,13 +8334,13 @@
         <v>44</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="J206" s="0">
-        <v>951.19749999999999</v>
+        <v>264.68939999999998</v>
       </c>
     </row>
     <row r="207">
@@ -8261,19 +8360,19 @@
         <v>32</v>
       </c>
       <c r="F207" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G207" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="J207" s="0">
-        <v>316.12619999999998</v>
+        <v>257.6934</v>
       </c>
     </row>
     <row r="208">
@@ -8293,19 +8392,19 @@
         <v>32</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="J208" s="0">
-        <v>302.2124</v>
+        <v>214.37610000000001</v>
       </c>
     </row>
     <row r="209">
@@ -8325,19 +8424,19 @@
         <v>32</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G209" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="J209" s="0">
-        <v>294.96859999999998</v>
+        <v>190.58150000000001</v>
       </c>
     </row>
     <row r="210">
@@ -8351,25 +8450,25 @@
         <v>8</v>
       </c>
       <c r="D210" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E210" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G210" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="J210" s="0">
-        <v>291.27109999999999</v>
+        <v>10441.448200000001</v>
       </c>
     </row>
     <row r="211">
@@ -8383,10 +8482,10 @@
         <v>8</v>
       </c>
       <c r="D211" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E211" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F211" s="0" t="s">
         <v>35</v>
@@ -8395,13 +8494,13 @@
         <v>44</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="J211" s="0">
-        <v>264.68939999999998</v>
+        <v>9728.8516</v>
       </c>
     </row>
     <row r="212">
@@ -8415,25 +8514,25 @@
         <v>8</v>
       </c>
       <c r="D212" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E212" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F212" s="0" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G212" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="J212" s="0">
-        <v>257.6934</v>
+        <v>1533.4409000000001</v>
       </c>
     </row>
     <row r="213">
@@ -8447,25 +8546,25 @@
         <v>8</v>
       </c>
       <c r="D213" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E213" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G213" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="J213" s="0">
-        <v>214.37610000000001</v>
+        <v>1358.2428</v>
       </c>
     </row>
     <row r="214">
@@ -8479,25 +8578,25 @@
         <v>8</v>
       </c>
       <c r="D214" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E214" s="0" t="s">
         <v>32</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G214" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="J214" s="0">
-        <v>190.58150000000001</v>
+        <v>452.1069</v>
       </c>
     </row>
     <row r="215">
@@ -8514,22 +8613,22 @@
         <v>28</v>
       </c>
       <c r="E215" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F215" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G215" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="J215" s="0">
-        <v>10441.448200000001</v>
+        <v>439.75790000000001</v>
       </c>
     </row>
     <row r="216">
@@ -8546,22 +8645,22 @@
         <v>28</v>
       </c>
       <c r="E216" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G216" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="J216" s="0">
-        <v>9728.8516</v>
+        <v>376.52229999999997</v>
       </c>
     </row>
     <row r="217">
@@ -8578,22 +8677,22 @@
         <v>28</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G217" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="J217" s="0">
-        <v>1533.4409000000001</v>
+        <v>375.43979999999999</v>
       </c>
     </row>
     <row r="218">
@@ -8610,7 +8709,7 @@
         <v>28</v>
       </c>
       <c r="E218" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F218" s="0" t="s">
         <v>35</v>
@@ -8619,13 +8718,13 @@
         <v>44</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="J218" s="0">
-        <v>1358.2428</v>
+        <v>373.55439999999999</v>
       </c>
     </row>
     <row r="219">
@@ -8645,19 +8744,19 @@
         <v>32</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G219" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="J219" s="0">
-        <v>452.1069</v>
+        <v>302.76659999999998</v>
       </c>
     </row>
     <row r="220">
@@ -8677,19 +8776,19 @@
         <v>32</v>
       </c>
       <c r="F220" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G220" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="J220" s="0">
-        <v>439.75790000000001</v>
+        <v>300.86579999999998</v>
       </c>
     </row>
     <row r="221">
@@ -8709,19 +8808,19 @@
         <v>32</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G221" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="J221" s="0">
-        <v>376.52229999999997</v>
+        <v>300.18029999999999</v>
       </c>
     </row>
     <row r="222">
@@ -8729,31 +8828,31 @@
         <v>1</v>
       </c>
       <c r="B222" s="0" t="s">
-        <v>3</v>
+        <v>437</v>
       </c>
       <c r="C222" s="0" t="s">
-        <v>8</v>
+        <v>438</v>
       </c>
       <c r="D222" s="0" t="s">
-        <v>28</v>
+        <v>442</v>
       </c>
       <c r="E222" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G222" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>235</v>
+        <v>472</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>431</v>
+        <v>514</v>
       </c>
       <c r="J222" s="0">
-        <v>375.43979999999999</v>
+        <v>12892.7021</v>
       </c>
     </row>
     <row r="223">
@@ -8761,16 +8860,16 @@
         <v>1</v>
       </c>
       <c r="B223" s="0" t="s">
-        <v>3</v>
+        <v>437</v>
       </c>
       <c r="C223" s="0" t="s">
-        <v>8</v>
+        <v>438</v>
       </c>
       <c r="D223" s="0" t="s">
-        <v>28</v>
+        <v>442</v>
       </c>
       <c r="E223" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F223" s="0" t="s">
         <v>35</v>
@@ -8779,13 +8878,13 @@
         <v>44</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>236</v>
+        <v>473</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>432</v>
+        <v>515</v>
       </c>
       <c r="J223" s="0">
-        <v>373.55439999999999</v>
+        <v>10694.238300000001</v>
       </c>
     </row>
     <row r="224">
@@ -8793,31 +8892,31 @@
         <v>1</v>
       </c>
       <c r="B224" s="0" t="s">
-        <v>3</v>
+        <v>437</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>8</v>
+        <v>438</v>
       </c>
       <c r="D224" s="0" t="s">
-        <v>28</v>
+        <v>442</v>
       </c>
       <c r="E224" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G224" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>237</v>
+        <v>474</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>433</v>
+        <v>516</v>
       </c>
       <c r="J224" s="0">
-        <v>302.76659999999998</v>
+        <v>2047.9614999999999</v>
       </c>
     </row>
     <row r="225">
@@ -8825,31 +8924,31 @@
         <v>1</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>3</v>
+        <v>437</v>
       </c>
       <c r="C225" s="0" t="s">
-        <v>8</v>
+        <v>438</v>
       </c>
       <c r="D225" s="0" t="s">
-        <v>28</v>
+        <v>442</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H225" s="0" t="s">
-        <v>238</v>
+        <v>475</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>434</v>
+        <v>517</v>
       </c>
       <c r="J225" s="0">
-        <v>300.86579999999998</v>
+        <v>910.678</v>
       </c>
     </row>
     <row r="226">
@@ -8857,31 +8956,31 @@
         <v>1</v>
       </c>
       <c r="B226" s="0" t="s">
-        <v>3</v>
+        <v>437</v>
       </c>
       <c r="C226" s="0" t="s">
-        <v>8</v>
+        <v>438</v>
       </c>
       <c r="D226" s="0" t="s">
-        <v>28</v>
+        <v>442</v>
       </c>
       <c r="E226" s="0" t="s">
         <v>32</v>
       </c>
       <c r="F226" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G226" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>239</v>
+        <v>476</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>435</v>
+        <v>518</v>
       </c>
       <c r="J226" s="0">
-        <v>300.18029999999999</v>
+        <v>597.62959999999998</v>
       </c>
     </row>
     <row r="227">
@@ -8898,22 +8997,22 @@
         <v>442</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="J227" s="0">
-        <v>12892.7021</v>
+        <v>568.2056</v>
       </c>
     </row>
     <row r="228">
@@ -8930,22 +9029,22 @@
         <v>442</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G228" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="J228" s="0">
-        <v>10694.238300000001</v>
+        <v>504.64819999999998</v>
       </c>
     </row>
     <row r="229">
@@ -8962,22 +9061,22 @@
         <v>442</v>
       </c>
       <c r="E229" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G229" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="J229" s="0">
-        <v>2047.9614999999999</v>
+        <v>489.4178</v>
       </c>
     </row>
     <row r="230">
@@ -8994,7 +9093,7 @@
         <v>442</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F230" s="0" t="s">
         <v>35</v>
@@ -9003,13 +9102,13 @@
         <v>44</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="J230" s="0">
-        <v>910.678</v>
+        <v>476.15269999999998</v>
       </c>
     </row>
     <row r="231">
@@ -9029,19 +9128,19 @@
         <v>32</v>
       </c>
       <c r="F231" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="J231" s="0">
-        <v>597.62959999999998</v>
+        <v>370.15899999999999</v>
       </c>
     </row>
     <row r="232">
@@ -9061,19 +9160,19 @@
         <v>32</v>
       </c>
       <c r="F232" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G232" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="J232" s="0">
-        <v>568.2056</v>
+        <v>366.79430000000002</v>
       </c>
     </row>
     <row r="233">
@@ -9093,19 +9192,19 @@
         <v>32</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G233" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="J233" s="0">
-        <v>504.64819999999998</v>
+        <v>340.95030000000003</v>
       </c>
     </row>
     <row r="234">

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="18774" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="22916" uniqueCount="559">
   <si>
     <t>Year</t>
   </si>
@@ -4357,7 +4357,7 @@
         <v>526</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F82" s="0" t="s">
         <v>34</v>
@@ -4366,13 +4366,13 @@
         <v>43</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="J82" s="0">
-        <v>1567.0791999999999</v>
+        <v>388.74549999999999</v>
       </c>
     </row>
     <row r="83">
@@ -4389,22 +4389,22 @@
         <v>526</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J83" s="0">
-        <v>1003.1186</v>
+        <v>308.16899999999998</v>
       </c>
     </row>
     <row r="84">
@@ -4424,19 +4424,19 @@
         <v>32</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G84" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J84" s="0">
-        <v>388.74549999999999</v>
+        <v>305.76100000000002</v>
       </c>
     </row>
     <row r="85">
@@ -4456,19 +4456,19 @@
         <v>32</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G85" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J85" s="0">
-        <v>308.16899999999998</v>
+        <v>304.48329999999999</v>
       </c>
     </row>
     <row r="86">
@@ -4488,19 +4488,19 @@
         <v>32</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="J86" s="0">
-        <v>305.76100000000002</v>
+        <v>297.43759999999998</v>
       </c>
     </row>
     <row r="87">
@@ -4520,19 +4520,19 @@
         <v>32</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J87" s="0">
-        <v>304.48329999999999</v>
+        <v>283.1619</v>
       </c>
     </row>
     <row r="88">
@@ -4552,19 +4552,19 @@
         <v>32</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G88" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="J88" s="0">
-        <v>297.43759999999998</v>
+        <v>247.529</v>
       </c>
     </row>
     <row r="89">
@@ -4584,19 +4584,19 @@
         <v>32</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J89" s="0">
-        <v>283.1619</v>
+        <v>231.5712</v>
       </c>
     </row>
     <row r="90">
@@ -4610,25 +4610,25 @@
         <v>438</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J90" s="0">
-        <v>247.529</v>
+        <v>1517.5046</v>
       </c>
     </row>
     <row r="91">
@@ -4642,25 +4642,25 @@
         <v>438</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G91" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J91" s="0">
-        <v>231.5712</v>
+        <v>1414.645</v>
       </c>
     </row>
     <row r="92">
@@ -4677,7 +4677,7 @@
         <v>527</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F92" s="0" t="s">
         <v>34</v>
@@ -4686,13 +4686,13 @@
         <v>43</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="J92" s="0">
-        <v>1517.5046</v>
+        <v>385.28089999999998</v>
       </c>
     </row>
     <row r="93">
@@ -4709,22 +4709,22 @@
         <v>527</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J93" s="0">
-        <v>1414.645</v>
+        <v>310.61110000000002</v>
       </c>
     </row>
     <row r="94">
@@ -4744,19 +4744,19 @@
         <v>32</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G94" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="J94" s="0">
-        <v>385.28089999999998</v>
+        <v>277.84199999999999</v>
       </c>
     </row>
     <row r="95">
@@ -4776,19 +4776,19 @@
         <v>32</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G95" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>458</v>
+        <v>63</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J95" s="0">
-        <v>310.61110000000002</v>
+        <v>223.45169999999999</v>
       </c>
     </row>
     <row r="96">
@@ -4802,25 +4802,25 @@
         <v>438</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G96" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J96" s="0">
-        <v>277.84199999999999</v>
+        <v>10215.762699999999</v>
       </c>
     </row>
     <row r="97">
@@ -4834,25 +4834,25 @@
         <v>438</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>63</v>
+        <v>461</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="J97" s="0">
-        <v>223.45169999999999</v>
+        <v>8851.0136999999995</v>
       </c>
     </row>
     <row r="98">
@@ -4869,7 +4869,7 @@
         <v>528</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F98" s="0" t="s">
         <v>34</v>
@@ -4878,13 +4878,13 @@
         <v>43</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="J98" s="0">
-        <v>10215.762699999999</v>
+        <v>1106.4232</v>
       </c>
     </row>
     <row r="99">
@@ -4901,7 +4901,7 @@
         <v>528</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F99" s="0" t="s">
         <v>35</v>
@@ -4910,13 +4910,13 @@
         <v>44</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="J99" s="0">
-        <v>8851.0136999999995</v>
+        <v>909.94200000000001</v>
       </c>
     </row>
     <row r="100">
@@ -4933,7 +4933,7 @@
         <v>528</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F100" s="0" t="s">
         <v>34</v>
@@ -4942,13 +4942,13 @@
         <v>43</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="J100" s="0">
-        <v>1106.4232</v>
+        <v>316.77910000000003</v>
       </c>
     </row>
     <row r="101">
@@ -4965,22 +4965,22 @@
         <v>528</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="J101" s="0">
-        <v>909.94200000000001</v>
+        <v>284.43700000000001</v>
       </c>
     </row>
     <row r="102">
@@ -5000,19 +5000,19 @@
         <v>32</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G102" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="J102" s="0">
-        <v>316.77910000000003</v>
+        <v>282.07659999999999</v>
       </c>
     </row>
     <row r="103">
@@ -5032,19 +5032,19 @@
         <v>32</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G103" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="J103" s="0">
-        <v>284.43700000000001</v>
+        <v>261.52760000000001</v>
       </c>
     </row>
     <row r="104">
@@ -5064,19 +5064,19 @@
         <v>32</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="J104" s="0">
-        <v>282.07659999999999</v>
+        <v>248.01570000000001</v>
       </c>
     </row>
     <row r="105">
@@ -5096,19 +5096,19 @@
         <v>32</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="J105" s="0">
-        <v>261.52760000000001</v>
+        <v>246.53380000000001</v>
       </c>
     </row>
     <row r="106">
@@ -5128,19 +5128,19 @@
         <v>32</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G106" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J106" s="0">
-        <v>248.01570000000001</v>
+        <v>228.9768</v>
       </c>
     </row>
     <row r="107">
@@ -5160,19 +5160,19 @@
         <v>32</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="J107" s="0">
-        <v>246.53380000000001</v>
+        <v>216.21680000000001</v>
       </c>
     </row>
     <row r="108">
@@ -5183,28 +5183,28 @@
         <v>3</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>438</v>
+        <v>7</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>528</v>
+        <v>19</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>470</v>
+        <v>123</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>557</v>
+        <v>319</v>
       </c>
       <c r="J108" s="0">
-        <v>228.9768</v>
+        <v>10261.8174</v>
       </c>
     </row>
     <row r="109">
@@ -5215,28 +5215,28 @@
         <v>3</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>438</v>
+        <v>7</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>528</v>
+        <v>19</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G109" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>471</v>
+        <v>124</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>558</v>
+        <v>320</v>
       </c>
       <c r="J109" s="0">
-        <v>216.21680000000001</v>
+        <v>9826.5293000000001</v>
       </c>
     </row>
     <row r="110">
@@ -5253,7 +5253,7 @@
         <v>19</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F110" s="0" t="s">
         <v>34</v>
@@ -5262,13 +5262,13 @@
         <v>43</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J110" s="0">
-        <v>10261.8174</v>
+        <v>310.85700000000003</v>
       </c>
     </row>
     <row r="111">
@@ -5285,22 +5285,22 @@
         <v>19</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J111" s="0">
-        <v>9826.5293000000001</v>
+        <v>294.82119999999998</v>
       </c>
     </row>
     <row r="112">
@@ -5320,19 +5320,19 @@
         <v>32</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G112" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J112" s="0">
-        <v>310.85700000000003</v>
+        <v>290.76960000000003</v>
       </c>
     </row>
     <row r="113">
@@ -5352,19 +5352,19 @@
         <v>32</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G113" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J113" s="0">
-        <v>294.82119999999998</v>
+        <v>273.49590000000001</v>
       </c>
     </row>
     <row r="114">
@@ -5384,19 +5384,19 @@
         <v>32</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J114" s="0">
-        <v>290.76960000000003</v>
+        <v>242.22909999999999</v>
       </c>
     </row>
     <row r="115">
@@ -5416,19 +5416,19 @@
         <v>32</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J115" s="0">
-        <v>273.49590000000001</v>
+        <v>238.70050000000001</v>
       </c>
     </row>
     <row r="116">
@@ -5448,19 +5448,19 @@
         <v>32</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G116" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J116" s="0">
-        <v>242.22909999999999</v>
+        <v>227.2551</v>
       </c>
     </row>
     <row r="117">
@@ -5480,19 +5480,19 @@
         <v>32</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G117" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J117" s="0">
-        <v>238.70050000000001</v>
+        <v>214.56540000000001</v>
       </c>
     </row>
     <row r="118">
@@ -5506,25 +5506,25 @@
         <v>7</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J118" s="0">
-        <v>227.2551</v>
+        <v>9905.6357000000007</v>
       </c>
     </row>
     <row r="119">
@@ -5538,25 +5538,25 @@
         <v>7</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G119" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J119" s="0">
-        <v>214.56540000000001</v>
+        <v>8499.6309000000001</v>
       </c>
     </row>
     <row r="120">
@@ -5573,7 +5573,7 @@
         <v>20</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F120" s="0" t="s">
         <v>34</v>
@@ -5582,13 +5582,13 @@
         <v>43</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J120" s="0">
-        <v>9905.6357000000007</v>
+        <v>1404.5636</v>
       </c>
     </row>
     <row r="121">
@@ -5605,22 +5605,22 @@
         <v>20</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J121" s="0">
-        <v>8499.6309000000001</v>
+        <v>315.27960000000002</v>
       </c>
     </row>
     <row r="122">
@@ -5637,22 +5637,22 @@
         <v>20</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G122" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J122" s="0">
-        <v>1404.5636</v>
+        <v>302.22129999999999</v>
       </c>
     </row>
     <row r="123">
@@ -5672,19 +5672,19 @@
         <v>32</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J123" s="0">
-        <v>315.27960000000002</v>
+        <v>266.9862</v>
       </c>
     </row>
     <row r="124">
@@ -5704,19 +5704,19 @@
         <v>32</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G124" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J124" s="0">
-        <v>302.22129999999999</v>
+        <v>264.11059999999998</v>
       </c>
     </row>
     <row r="125">
@@ -5736,19 +5736,19 @@
         <v>32</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J125" s="0">
-        <v>266.9862</v>
+        <v>247.79859999999999</v>
       </c>
     </row>
     <row r="126">
@@ -5768,19 +5768,19 @@
         <v>32</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J126" s="0">
-        <v>264.11059999999998</v>
+        <v>239.36019999999999</v>
       </c>
     </row>
     <row r="127">
@@ -5800,19 +5800,19 @@
         <v>32</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G127" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J127" s="0">
-        <v>247.79859999999999</v>
+        <v>208.72989999999999</v>
       </c>
     </row>
     <row r="128">
@@ -5832,19 +5832,19 @@
         <v>32</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G128" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J128" s="0">
-        <v>239.36019999999999</v>
+        <v>199.44909999999999</v>
       </c>
     </row>
     <row r="129">
@@ -5858,25 +5858,25 @@
         <v>7</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J129" s="0">
-        <v>208.72989999999999</v>
+        <v>9596.9883000000009</v>
       </c>
     </row>
     <row r="130">
@@ -5890,25 +5890,25 @@
         <v>7</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E130" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J130" s="0">
-        <v>199.44909999999999</v>
+        <v>8798.1787000000004</v>
       </c>
     </row>
     <row r="131">
@@ -5925,7 +5925,7 @@
         <v>21</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F131" s="0" t="s">
         <v>34</v>
@@ -5934,13 +5934,13 @@
         <v>43</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J131" s="0">
-        <v>9596.9883000000009</v>
+        <v>1321.1365000000001</v>
       </c>
     </row>
     <row r="132">
@@ -5957,7 +5957,7 @@
         <v>21</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F132" s="0" t="s">
         <v>35</v>
@@ -5966,13 +5966,13 @@
         <v>44</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J132" s="0">
-        <v>8798.1787000000004</v>
+        <v>959.9144</v>
       </c>
     </row>
     <row r="133">
@@ -5989,7 +5989,7 @@
         <v>21</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F133" s="0" t="s">
         <v>34</v>
@@ -5998,13 +5998,13 @@
         <v>43</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J133" s="0">
-        <v>1321.1365000000001</v>
+        <v>309.23169999999999</v>
       </c>
     </row>
     <row r="134">
@@ -6021,22 +6021,22 @@
         <v>21</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G134" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J134" s="0">
-        <v>959.9144</v>
+        <v>301.12470000000002</v>
       </c>
     </row>
     <row r="135">
@@ -6056,19 +6056,19 @@
         <v>32</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J135" s="0">
-        <v>309.23169999999999</v>
+        <v>296.84010000000001</v>
       </c>
     </row>
     <row r="136">
@@ -6088,19 +6088,19 @@
         <v>32</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G136" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J136" s="0">
-        <v>301.12470000000002</v>
+        <v>288.2115</v>
       </c>
     </row>
     <row r="137">
@@ -6120,19 +6120,19 @@
         <v>32</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J137" s="0">
-        <v>296.84010000000001</v>
+        <v>274.3639</v>
       </c>
     </row>
     <row r="138">
@@ -6152,19 +6152,19 @@
         <v>32</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J138" s="0">
-        <v>288.2115</v>
+        <v>260.00229999999999</v>
       </c>
     </row>
     <row r="139">
@@ -6184,19 +6184,19 @@
         <v>32</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J139" s="0">
-        <v>274.3639</v>
+        <v>246.21190000000001</v>
       </c>
     </row>
     <row r="140">
@@ -6216,19 +6216,19 @@
         <v>32</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G140" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J140" s="0">
-        <v>260.00229999999999</v>
+        <v>180.47190000000001</v>
       </c>
     </row>
     <row r="141">
@@ -6242,25 +6242,25 @@
         <v>7</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J141" s="0">
-        <v>246.21190000000001</v>
+        <v>9836.6807000000008</v>
       </c>
     </row>
     <row r="142">
@@ -6274,25 +6274,25 @@
         <v>7</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E142" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G142" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="J142" s="0">
-        <v>180.47190000000001</v>
+        <v>908.87840000000006</v>
       </c>
     </row>
     <row r="143">
@@ -6309,22 +6309,22 @@
         <v>22</v>
       </c>
       <c r="E143" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J143" s="0">
-        <v>9836.6807000000008</v>
+        <v>840.46699999999999</v>
       </c>
     </row>
     <row r="144">
@@ -6341,7 +6341,7 @@
         <v>22</v>
       </c>
       <c r="E144" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F144" s="0" t="s">
         <v>34</v>
@@ -6350,13 +6350,13 @@
         <v>43</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J144" s="0">
-        <v>908.87840000000006</v>
+        <v>385.22919999999999</v>
       </c>
     </row>
     <row r="145">
@@ -6373,22 +6373,22 @@
         <v>22</v>
       </c>
       <c r="E145" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G145" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J145" s="0">
-        <v>840.46699999999999</v>
+        <v>310.47890000000001</v>
       </c>
     </row>
     <row r="146">
@@ -6408,19 +6408,19 @@
         <v>32</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G146" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J146" s="0">
-        <v>385.22919999999999</v>
+        <v>300.91699999999997</v>
       </c>
     </row>
     <row r="147">
@@ -6440,19 +6440,19 @@
         <v>32</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J147" s="0">
-        <v>310.47890000000001</v>
+        <v>285.7113</v>
       </c>
     </row>
     <row r="148">
@@ -6472,19 +6472,19 @@
         <v>32</v>
       </c>
       <c r="F148" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G148" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J148" s="0">
-        <v>300.91699999999997</v>
+        <v>255.1182</v>
       </c>
     </row>
     <row r="149">
@@ -6504,19 +6504,19 @@
         <v>32</v>
       </c>
       <c r="F149" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G149" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J149" s="0">
-        <v>285.7113</v>
+        <v>251.63229999999999</v>
       </c>
     </row>
     <row r="150">
@@ -6536,19 +6536,19 @@
         <v>32</v>
       </c>
       <c r="F150" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G150" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J150" s="0">
-        <v>255.1182</v>
+        <v>241.47989999999999</v>
       </c>
     </row>
     <row r="151">
@@ -6568,19 +6568,19 @@
         <v>32</v>
       </c>
       <c r="F151" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G151" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J151" s="0">
-        <v>251.63229999999999</v>
+        <v>239.88820000000001</v>
       </c>
     </row>
     <row r="152">
@@ -6591,28 +6591,28 @@
         <v>3</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E152" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G152" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J152" s="0">
-        <v>241.47989999999999</v>
+        <v>10661.891600000001</v>
       </c>
     </row>
     <row r="153">
@@ -6623,28 +6623,28 @@
         <v>3</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D153" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E153" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F153" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G153" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H153" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="J153" s="0">
-        <v>239.88820000000001</v>
+        <v>7643.7520000000004</v>
       </c>
     </row>
     <row r="154">
@@ -6661,7 +6661,7 @@
         <v>23</v>
       </c>
       <c r="E154" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F154" s="0" t="s">
         <v>34</v>
@@ -6670,13 +6670,13 @@
         <v>43</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J154" s="0">
-        <v>10661.891600000001</v>
+        <v>1539.2754</v>
       </c>
     </row>
     <row r="155">
@@ -6693,7 +6693,7 @@
         <v>23</v>
       </c>
       <c r="E155" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F155" s="0" t="s">
         <v>35</v>
@@ -6702,13 +6702,13 @@
         <v>44</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="J155" s="0">
-        <v>7643.7520000000004</v>
+        <v>1393.9193</v>
       </c>
     </row>
     <row r="156">
@@ -6725,7 +6725,7 @@
         <v>23</v>
       </c>
       <c r="E156" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F156" s="0" t="s">
         <v>34</v>
@@ -6734,13 +6734,13 @@
         <v>43</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J156" s="0">
-        <v>1539.2754</v>
+        <v>457.66739999999999</v>
       </c>
     </row>
     <row r="157">
@@ -6757,22 +6757,22 @@
         <v>23</v>
       </c>
       <c r="E157" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F157" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G157" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H157" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J157" s="0">
-        <v>1393.9193</v>
+        <v>419.16669999999999</v>
       </c>
     </row>
     <row r="158">
@@ -6792,19 +6792,19 @@
         <v>32</v>
       </c>
       <c r="F158" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G158" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H158" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J158" s="0">
-        <v>457.66739999999999</v>
+        <v>417.49169999999998</v>
       </c>
     </row>
     <row r="159">
@@ -6824,19 +6824,19 @@
         <v>32</v>
       </c>
       <c r="F159" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G159" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H159" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J159" s="0">
-        <v>419.16669999999999</v>
+        <v>399.00799999999998</v>
       </c>
     </row>
     <row r="160">
@@ -6856,19 +6856,19 @@
         <v>32</v>
       </c>
       <c r="F160" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G160" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H160" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J160" s="0">
-        <v>417.49169999999998</v>
+        <v>361.1662</v>
       </c>
     </row>
     <row r="161">
@@ -6888,19 +6888,19 @@
         <v>32</v>
       </c>
       <c r="F161" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G161" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H161" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="J161" s="0">
-        <v>399.00799999999998</v>
+        <v>329.83010000000002</v>
       </c>
     </row>
     <row r="162">
@@ -6920,19 +6920,19 @@
         <v>32</v>
       </c>
       <c r="F162" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G162" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H162" s="0" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J162" s="0">
-        <v>361.1662</v>
+        <v>311.19600000000003</v>
       </c>
     </row>
     <row r="163">
@@ -6952,19 +6952,19 @@
         <v>32</v>
       </c>
       <c r="F163" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G163" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H163" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J163" s="0">
-        <v>329.83010000000002</v>
+        <v>291.23480000000001</v>
       </c>
     </row>
     <row r="164">
@@ -6978,25 +6978,25 @@
         <v>8</v>
       </c>
       <c r="D164" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E164" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F164" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G164" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H164" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J164" s="0">
-        <v>311.19600000000003</v>
+        <v>9127.5985999999994</v>
       </c>
     </row>
     <row r="165">
@@ -7010,25 +7010,25 @@
         <v>8</v>
       </c>
       <c r="D165" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E165" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F165" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G165" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H165" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J165" s="0">
-        <v>291.23480000000001</v>
+        <v>8554.8642999999993</v>
       </c>
     </row>
     <row r="166">
@@ -7045,7 +7045,7 @@
         <v>24</v>
       </c>
       <c r="E166" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F166" s="0" t="s">
         <v>34</v>
@@ -7054,13 +7054,13 @@
         <v>43</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J166" s="0">
-        <v>9127.5985999999994</v>
+        <v>1414.848</v>
       </c>
     </row>
     <row r="167">
@@ -7077,7 +7077,7 @@
         <v>24</v>
       </c>
       <c r="E167" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F167" s="0" t="s">
         <v>35</v>
@@ -7086,13 +7086,13 @@
         <v>44</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J167" s="0">
-        <v>8554.8642999999993</v>
+        <v>752.67660000000001</v>
       </c>
     </row>
     <row r="168">
@@ -7109,7 +7109,7 @@
         <v>24</v>
       </c>
       <c r="E168" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F168" s="0" t="s">
         <v>34</v>
@@ -7118,13 +7118,13 @@
         <v>43</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J168" s="0">
-        <v>1414.848</v>
+        <v>348.73090000000002</v>
       </c>
     </row>
     <row r="169">
@@ -7141,22 +7141,22 @@
         <v>24</v>
       </c>
       <c r="E169" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F169" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G169" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H169" s="0" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J169" s="0">
-        <v>752.67660000000001</v>
+        <v>307.04939999999999</v>
       </c>
     </row>
     <row r="170">
@@ -7176,19 +7176,19 @@
         <v>32</v>
       </c>
       <c r="F170" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G170" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H170" s="0" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J170" s="0">
-        <v>348.73090000000002</v>
+        <v>280.97919999999999</v>
       </c>
     </row>
     <row r="171">
@@ -7208,19 +7208,19 @@
         <v>32</v>
       </c>
       <c r="F171" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G171" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H171" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J171" s="0">
-        <v>307.04939999999999</v>
+        <v>265.1284</v>
       </c>
     </row>
     <row r="172">
@@ -7240,19 +7240,19 @@
         <v>32</v>
       </c>
       <c r="F172" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G172" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H172" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J172" s="0">
-        <v>280.97919999999999</v>
+        <v>249.8895</v>
       </c>
     </row>
     <row r="173">
@@ -7272,19 +7272,19 @@
         <v>32</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G173" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J173" s="0">
-        <v>265.1284</v>
+        <v>215.3955</v>
       </c>
     </row>
     <row r="174">
@@ -7304,19 +7304,19 @@
         <v>32</v>
       </c>
       <c r="F174" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G174" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J174" s="0">
-        <v>249.8895</v>
+        <v>213.6302</v>
       </c>
     </row>
     <row r="175">
@@ -7336,19 +7336,19 @@
         <v>32</v>
       </c>
       <c r="F175" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G175" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J175" s="0">
-        <v>215.3955</v>
+        <v>193.54920000000001</v>
       </c>
     </row>
     <row r="176">
@@ -7362,25 +7362,25 @@
         <v>8</v>
       </c>
       <c r="D176" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E176" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G176" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J176" s="0">
-        <v>213.6302</v>
+        <v>9254.9814000000006</v>
       </c>
     </row>
     <row r="177">
@@ -7394,25 +7394,25 @@
         <v>8</v>
       </c>
       <c r="D177" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E177" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G177" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J177" s="0">
-        <v>193.54920000000001</v>
+        <v>8396.3974999999991</v>
       </c>
     </row>
     <row r="178">
@@ -7429,7 +7429,7 @@
         <v>25</v>
       </c>
       <c r="E178" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F178" s="0" t="s">
         <v>34</v>
@@ -7438,13 +7438,13 @@
         <v>43</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J178" s="0">
-        <v>9254.9814000000006</v>
+        <v>1087.1931999999999</v>
       </c>
     </row>
     <row r="179">
@@ -7461,7 +7461,7 @@
         <v>25</v>
       </c>
       <c r="E179" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F179" s="0" t="s">
         <v>35</v>
@@ -7470,13 +7470,13 @@
         <v>44</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J179" s="0">
-        <v>8396.3974999999991</v>
+        <v>1026.0048999999999</v>
       </c>
     </row>
     <row r="180">
@@ -7493,7 +7493,7 @@
         <v>25</v>
       </c>
       <c r="E180" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F180" s="0" t="s">
         <v>34</v>
@@ -7502,13 +7502,13 @@
         <v>43</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J180" s="0">
-        <v>1087.1931999999999</v>
+        <v>328.2697</v>
       </c>
     </row>
     <row r="181">
@@ -7525,22 +7525,22 @@
         <v>25</v>
       </c>
       <c r="E181" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F181" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G181" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J181" s="0">
-        <v>1026.0048999999999</v>
+        <v>306.13749999999999</v>
       </c>
     </row>
     <row r="182">
@@ -7560,19 +7560,19 @@
         <v>32</v>
       </c>
       <c r="F182" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G182" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H182" s="0" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J182" s="0">
-        <v>328.2697</v>
+        <v>302.69369999999998</v>
       </c>
     </row>
     <row r="183">
@@ -7592,19 +7592,19 @@
         <v>32</v>
       </c>
       <c r="F183" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G183" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J183" s="0">
-        <v>306.13749999999999</v>
+        <v>296.63529999999997</v>
       </c>
     </row>
     <row r="184">
@@ -7624,19 +7624,19 @@
         <v>32</v>
       </c>
       <c r="F184" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G184" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J184" s="0">
-        <v>302.69369999999998</v>
+        <v>292.96969999999999</v>
       </c>
     </row>
     <row r="185">
@@ -7656,19 +7656,19 @@
         <v>32</v>
       </c>
       <c r="F185" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G185" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J185" s="0">
-        <v>296.63529999999997</v>
+        <v>267.35629999999998</v>
       </c>
     </row>
     <row r="186">
@@ -7688,19 +7688,19 @@
         <v>32</v>
       </c>
       <c r="F186" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G186" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H186" s="0" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="J186" s="0">
-        <v>292.96969999999999</v>
+        <v>165.21969999999999</v>
       </c>
     </row>
     <row r="187">
@@ -7714,25 +7714,25 @@
         <v>8</v>
       </c>
       <c r="D187" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G187" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H187" s="0" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="J187" s="0">
-        <v>267.35629999999998</v>
+        <v>1713.3430000000001</v>
       </c>
     </row>
     <row r="188">
@@ -7746,25 +7746,25 @@
         <v>8</v>
       </c>
       <c r="D188" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E188" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="J188" s="0">
-        <v>165.21969999999999</v>
+        <v>1254.9603</v>
       </c>
     </row>
     <row r="189">
@@ -7781,7 +7781,7 @@
         <v>26</v>
       </c>
       <c r="E189" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F189" s="0" t="s">
         <v>34</v>
@@ -7790,13 +7790,13 @@
         <v>43</v>
       </c>
       <c r="H189" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J189" s="0">
-        <v>1713.3430000000001</v>
+        <v>412.1336</v>
       </c>
     </row>
     <row r="190">
@@ -7813,22 +7813,22 @@
         <v>26</v>
       </c>
       <c r="E190" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F190" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G190" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J190" s="0">
-        <v>1254.9603</v>
+        <v>395.3304</v>
       </c>
     </row>
     <row r="191">
@@ -7848,19 +7848,19 @@
         <v>32</v>
       </c>
       <c r="F191" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G191" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J191" s="0">
-        <v>412.1336</v>
+        <v>314.40159999999997</v>
       </c>
     </row>
     <row r="192">
@@ -7880,19 +7880,19 @@
         <v>32</v>
       </c>
       <c r="F192" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G192" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J192" s="0">
-        <v>395.3304</v>
+        <v>306.70960000000002</v>
       </c>
     </row>
     <row r="193">
@@ -7912,19 +7912,19 @@
         <v>32</v>
       </c>
       <c r="F193" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G193" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J193" s="0">
-        <v>314.40159999999997</v>
+        <v>285.86070000000001</v>
       </c>
     </row>
     <row r="194">
@@ -7944,19 +7944,19 @@
         <v>32</v>
       </c>
       <c r="F194" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G194" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J194" s="0">
-        <v>306.70960000000002</v>
+        <v>284.4486</v>
       </c>
     </row>
     <row r="195">
@@ -7976,19 +7976,19 @@
         <v>32</v>
       </c>
       <c r="F195" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G195" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="J195" s="0">
-        <v>285.86070000000001</v>
+        <v>281.97449999999998</v>
       </c>
     </row>
     <row r="196">
@@ -8002,25 +8002,25 @@
         <v>8</v>
       </c>
       <c r="D196" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F196" s="0" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G196" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="J196" s="0">
-        <v>284.4486</v>
+        <v>9423.6895000000004</v>
       </c>
     </row>
     <row r="197">
@@ -8034,25 +8034,25 @@
         <v>8</v>
       </c>
       <c r="D197" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F197" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G197" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="J197" s="0">
-        <v>281.97449999999998</v>
+        <v>9234.3525000000009</v>
       </c>
     </row>
     <row r="198">
@@ -8069,7 +8069,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F198" s="0" t="s">
         <v>34</v>
@@ -8078,13 +8078,13 @@
         <v>43</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J198" s="0">
-        <v>9423.6895000000004</v>
+        <v>1208.9946</v>
       </c>
     </row>
     <row r="199">
@@ -8101,7 +8101,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F199" s="0" t="s">
         <v>35</v>
@@ -8110,13 +8110,13 @@
         <v>44</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J199" s="0">
-        <v>9234.3525000000009</v>
+        <v>951.19749999999999</v>
       </c>
     </row>
     <row r="200">
@@ -8133,7 +8133,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F200" s="0" t="s">
         <v>34</v>
@@ -8142,13 +8142,13 @@
         <v>43</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J200" s="0">
-        <v>1208.9946</v>
+        <v>316.12619999999998</v>
       </c>
     </row>
     <row r="201">
@@ -8165,22 +8165,22 @@
         <v>27</v>
       </c>
       <c r="E201" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G201" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J201" s="0">
-        <v>951.19749999999999</v>
+        <v>302.2124</v>
       </c>
     </row>
     <row r="202">
@@ -8200,19 +8200,19 @@
         <v>32</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G202" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J202" s="0">
-        <v>316.12619999999998</v>
+        <v>294.96859999999998</v>
       </c>
     </row>
     <row r="203">
@@ -8232,19 +8232,19 @@
         <v>32</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J203" s="0">
-        <v>302.2124</v>
+        <v>291.27109999999999</v>
       </c>
     </row>
     <row r="204">
@@ -8264,19 +8264,19 @@
         <v>32</v>
       </c>
       <c r="F204" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G204" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J204" s="0">
-        <v>294.96859999999998</v>
+        <v>264.68939999999998</v>
       </c>
     </row>
     <row r="205">
@@ -8296,19 +8296,19 @@
         <v>32</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G205" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J205" s="0">
-        <v>291.27109999999999</v>
+        <v>257.6934</v>
       </c>
     </row>
     <row r="206">
@@ -8328,19 +8328,19 @@
         <v>32</v>
       </c>
       <c r="F206" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G206" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J206" s="0">
-        <v>264.68939999999998</v>
+        <v>214.37610000000001</v>
       </c>
     </row>
     <row r="207">
@@ -8360,19 +8360,19 @@
         <v>32</v>
       </c>
       <c r="F207" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G207" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J207" s="0">
-        <v>257.6934</v>
+        <v>190.58150000000001</v>
       </c>
     </row>
     <row r="208">
@@ -8386,25 +8386,25 @@
         <v>8</v>
       </c>
       <c r="D208" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E208" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J208" s="0">
-        <v>214.37610000000001</v>
+        <v>10441.448200000001</v>
       </c>
     </row>
     <row r="209">
@@ -8418,25 +8418,25 @@
         <v>8</v>
       </c>
       <c r="D209" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E209" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G209" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J209" s="0">
-        <v>190.58150000000001</v>
+        <v>9728.8516</v>
       </c>
     </row>
     <row r="210">
@@ -8453,7 +8453,7 @@
         <v>28</v>
       </c>
       <c r="E210" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F210" s="0" t="s">
         <v>34</v>
@@ -8462,13 +8462,13 @@
         <v>43</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J210" s="0">
-        <v>10441.448200000001</v>
+        <v>1533.4409000000001</v>
       </c>
     </row>
     <row r="211">
@@ -8485,7 +8485,7 @@
         <v>28</v>
       </c>
       <c r="E211" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F211" s="0" t="s">
         <v>35</v>
@@ -8494,13 +8494,13 @@
         <v>44</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J211" s="0">
-        <v>9728.8516</v>
+        <v>1358.2428</v>
       </c>
     </row>
     <row r="212">
@@ -8517,7 +8517,7 @@
         <v>28</v>
       </c>
       <c r="E212" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F212" s="0" t="s">
         <v>34</v>
@@ -8526,13 +8526,13 @@
         <v>43</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J212" s="0">
-        <v>1533.4409000000001</v>
+        <v>452.1069</v>
       </c>
     </row>
     <row r="213">
@@ -8549,22 +8549,22 @@
         <v>28</v>
       </c>
       <c r="E213" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G213" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J213" s="0">
-        <v>1358.2428</v>
+        <v>439.75790000000001</v>
       </c>
     </row>
     <row r="214">
@@ -8584,19 +8584,19 @@
         <v>32</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J214" s="0">
-        <v>452.1069</v>
+        <v>376.52229999999997</v>
       </c>
     </row>
     <row r="215">
@@ -8616,19 +8616,19 @@
         <v>32</v>
       </c>
       <c r="F215" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G215" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J215" s="0">
-        <v>439.75790000000001</v>
+        <v>375.43979999999999</v>
       </c>
     </row>
     <row r="216">
@@ -8648,19 +8648,19 @@
         <v>32</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G216" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J216" s="0">
-        <v>376.52229999999997</v>
+        <v>373.55439999999999</v>
       </c>
     </row>
     <row r="217">
@@ -8680,19 +8680,19 @@
         <v>32</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G217" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J217" s="0">
-        <v>375.43979999999999</v>
+        <v>302.76659999999998</v>
       </c>
     </row>
     <row r="218">
@@ -8712,19 +8712,19 @@
         <v>32</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G218" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="J218" s="0">
-        <v>373.55439999999999</v>
+        <v>300.86579999999998</v>
       </c>
     </row>
     <row r="219">
@@ -8744,19 +8744,19 @@
         <v>32</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G219" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J219" s="0">
-        <v>302.76659999999998</v>
+        <v>300.18029999999999</v>
       </c>
     </row>
     <row r="220">
@@ -8764,31 +8764,31 @@
         <v>1</v>
       </c>
       <c r="B220" s="0" t="s">
-        <v>3</v>
+        <v>437</v>
       </c>
       <c r="C220" s="0" t="s">
-        <v>8</v>
+        <v>438</v>
       </c>
       <c r="D220" s="0" t="s">
-        <v>28</v>
+        <v>442</v>
       </c>
       <c r="E220" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F220" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G220" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>238</v>
+        <v>472</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>434</v>
+        <v>514</v>
       </c>
       <c r="J220" s="0">
-        <v>300.86579999999998</v>
+        <v>12892.7021</v>
       </c>
     </row>
     <row r="221">
@@ -8796,31 +8796,31 @@
         <v>1</v>
       </c>
       <c r="B221" s="0" t="s">
-        <v>3</v>
+        <v>437</v>
       </c>
       <c r="C221" s="0" t="s">
-        <v>8</v>
+        <v>438</v>
       </c>
       <c r="D221" s="0" t="s">
-        <v>28</v>
+        <v>442</v>
       </c>
       <c r="E221" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G221" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>239</v>
+        <v>473</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>435</v>
+        <v>515</v>
       </c>
       <c r="J221" s="0">
-        <v>300.18029999999999</v>
+        <v>10694.238300000001</v>
       </c>
     </row>
     <row r="222">
@@ -8837,7 +8837,7 @@
         <v>442</v>
       </c>
       <c r="E222" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F222" s="0" t="s">
         <v>34</v>
@@ -8846,13 +8846,13 @@
         <v>43</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J222" s="0">
-        <v>12892.7021</v>
+        <v>2047.9614999999999</v>
       </c>
     </row>
     <row r="223">
@@ -8869,7 +8869,7 @@
         <v>442</v>
       </c>
       <c r="E223" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F223" s="0" t="s">
         <v>35</v>
@@ -8878,13 +8878,13 @@
         <v>44</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J223" s="0">
-        <v>10694.238300000001</v>
+        <v>910.678</v>
       </c>
     </row>
     <row r="224">
@@ -8901,7 +8901,7 @@
         <v>442</v>
       </c>
       <c r="E224" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F224" s="0" t="s">
         <v>34</v>
@@ -8910,13 +8910,13 @@
         <v>43</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J224" s="0">
-        <v>2047.9614999999999</v>
+        <v>597.62959999999998</v>
       </c>
     </row>
     <row r="225">
@@ -8933,22 +8933,22 @@
         <v>442</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G225" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H225" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="J225" s="0">
-        <v>910.678</v>
+        <v>568.2056</v>
       </c>
     </row>
     <row r="226">
@@ -8968,19 +8968,19 @@
         <v>32</v>
       </c>
       <c r="F226" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G226" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J226" s="0">
-        <v>597.62959999999998</v>
+        <v>504.64819999999998</v>
       </c>
     </row>
     <row r="227">
@@ -9000,19 +9000,19 @@
         <v>32</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J227" s="0">
-        <v>568.2056</v>
+        <v>489.4178</v>
       </c>
     </row>
     <row r="228">
@@ -9032,19 +9032,19 @@
         <v>32</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G228" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="J228" s="0">
-        <v>504.64819999999998</v>
+        <v>370.15899999999999</v>
       </c>
     </row>
     <row r="229">
@@ -9064,19 +9064,19 @@
         <v>32</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G229" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="J229" s="0">
-        <v>489.4178</v>
+        <v>366.79430000000002</v>
       </c>
     </row>
     <row r="230">
@@ -9096,19 +9096,19 @@
         <v>32</v>
       </c>
       <c r="F230" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G230" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="J230" s="0">
-        <v>476.15269999999998</v>
+        <v>340.95030000000003</v>
       </c>
     </row>
     <row r="231">

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="22916" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="27058" uniqueCount="559">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="27058" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="29084" uniqueCount="559">
   <si>
     <t>Year</t>
   </si>
@@ -6894,13 +6894,13 @@
         <v>44</v>
       </c>
       <c r="H161" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J161" s="0">
-        <v>329.83010000000002</v>
+        <v>311.19600000000003</v>
       </c>
     </row>
     <row r="162">
@@ -6926,13 +6926,13 @@
         <v>44</v>
       </c>
       <c r="H162" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J162" s="0">
-        <v>311.19600000000003</v>
+        <v>291.23480000000001</v>
       </c>
     </row>
     <row r="163">
@@ -6946,25 +6946,25 @@
         <v>8</v>
       </c>
       <c r="D163" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E163" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F163" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G163" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H163" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J163" s="0">
-        <v>291.23480000000001</v>
+        <v>9127.5985999999994</v>
       </c>
     </row>
     <row r="164">
@@ -6984,19 +6984,19 @@
         <v>30</v>
       </c>
       <c r="F164" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G164" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H164" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J164" s="0">
-        <v>9127.5985999999994</v>
+        <v>8554.8642999999993</v>
       </c>
     </row>
     <row r="165">
@@ -7013,22 +7013,22 @@
         <v>24</v>
       </c>
       <c r="E165" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F165" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G165" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H165" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J165" s="0">
-        <v>8554.8642999999993</v>
+        <v>1414.848</v>
       </c>
     </row>
     <row r="166">
@@ -7048,19 +7048,19 @@
         <v>31</v>
       </c>
       <c r="F166" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G166" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J166" s="0">
-        <v>1414.848</v>
+        <v>752.67660000000001</v>
       </c>
     </row>
     <row r="167">
@@ -7077,22 +7077,22 @@
         <v>24</v>
       </c>
       <c r="E167" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F167" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G167" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J167" s="0">
-        <v>752.67660000000001</v>
+        <v>348.73090000000002</v>
       </c>
     </row>
     <row r="168">
@@ -7112,19 +7112,19 @@
         <v>32</v>
       </c>
       <c r="F168" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G168" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J168" s="0">
-        <v>348.73090000000002</v>
+        <v>307.04939999999999</v>
       </c>
     </row>
     <row r="169">
@@ -7144,19 +7144,19 @@
         <v>32</v>
       </c>
       <c r="F169" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G169" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H169" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J169" s="0">
-        <v>307.04939999999999</v>
+        <v>280.97919999999999</v>
       </c>
     </row>
     <row r="170">
@@ -7176,19 +7176,19 @@
         <v>32</v>
       </c>
       <c r="F170" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G170" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H170" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J170" s="0">
-        <v>280.97919999999999</v>
+        <v>265.1284</v>
       </c>
     </row>
     <row r="171">
@@ -7208,19 +7208,19 @@
         <v>32</v>
       </c>
       <c r="F171" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G171" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H171" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J171" s="0">
-        <v>265.1284</v>
+        <v>249.8895</v>
       </c>
     </row>
     <row r="172">
@@ -7240,19 +7240,19 @@
         <v>32</v>
       </c>
       <c r="F172" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G172" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H172" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J172" s="0">
-        <v>249.8895</v>
+        <v>215.3955</v>
       </c>
     </row>
     <row r="173">
@@ -7272,19 +7272,19 @@
         <v>32</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G173" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J173" s="0">
-        <v>215.3955</v>
+        <v>213.6302</v>
       </c>
     </row>
     <row r="174">
@@ -7304,19 +7304,19 @@
         <v>32</v>
       </c>
       <c r="F174" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G174" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J174" s="0">
-        <v>213.6302</v>
+        <v>193.54920000000001</v>
       </c>
     </row>
     <row r="175">
@@ -7330,25 +7330,25 @@
         <v>8</v>
       </c>
       <c r="D175" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E175" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F175" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G175" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J175" s="0">
-        <v>193.54920000000001</v>
+        <v>9254.9814000000006</v>
       </c>
     </row>
     <row r="176">
@@ -7368,19 +7368,19 @@
         <v>30</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G176" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J176" s="0">
-        <v>9254.9814000000006</v>
+        <v>8396.3974999999991</v>
       </c>
     </row>
     <row r="177">
@@ -7397,22 +7397,22 @@
         <v>25</v>
       </c>
       <c r="E177" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G177" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J177" s="0">
-        <v>8396.3974999999991</v>
+        <v>1087.1931999999999</v>
       </c>
     </row>
     <row r="178">
@@ -7432,19 +7432,19 @@
         <v>31</v>
       </c>
       <c r="F178" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G178" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J178" s="0">
-        <v>1087.1931999999999</v>
+        <v>1026.0048999999999</v>
       </c>
     </row>
     <row r="179">
@@ -7461,22 +7461,22 @@
         <v>25</v>
       </c>
       <c r="E179" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G179" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J179" s="0">
-        <v>1026.0048999999999</v>
+        <v>328.2697</v>
       </c>
     </row>
     <row r="180">
@@ -7496,19 +7496,19 @@
         <v>32</v>
       </c>
       <c r="F180" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G180" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J180" s="0">
-        <v>328.2697</v>
+        <v>306.13749999999999</v>
       </c>
     </row>
     <row r="181">
@@ -7528,19 +7528,19 @@
         <v>32</v>
       </c>
       <c r="F181" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G181" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J181" s="0">
-        <v>306.13749999999999</v>
+        <v>302.69369999999998</v>
       </c>
     </row>
     <row r="182">
@@ -7560,19 +7560,19 @@
         <v>32</v>
       </c>
       <c r="F182" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G182" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H182" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J182" s="0">
-        <v>302.69369999999998</v>
+        <v>296.63529999999997</v>
       </c>
     </row>
     <row r="183">
@@ -7592,19 +7592,19 @@
         <v>32</v>
       </c>
       <c r="F183" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G183" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J183" s="0">
-        <v>296.63529999999997</v>
+        <v>292.96969999999999</v>
       </c>
     </row>
     <row r="184">
@@ -7624,19 +7624,19 @@
         <v>32</v>
       </c>
       <c r="F184" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G184" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J184" s="0">
-        <v>292.96969999999999</v>
+        <v>267.35629999999998</v>
       </c>
     </row>
     <row r="185">
@@ -7656,19 +7656,19 @@
         <v>32</v>
       </c>
       <c r="F185" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G185" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J185" s="0">
-        <v>267.35629999999998</v>
+        <v>165.21969999999999</v>
       </c>
     </row>
     <row r="186">
@@ -7682,25 +7682,25 @@
         <v>8</v>
       </c>
       <c r="D186" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E186" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F186" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G186" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H186" s="0" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="J186" s="0">
-        <v>165.21969999999999</v>
+        <v>1713.3430000000001</v>
       </c>
     </row>
     <row r="187">
@@ -7720,19 +7720,19 @@
         <v>31</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G187" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H187" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J187" s="0">
-        <v>1713.3430000000001</v>
+        <v>1254.9603</v>
       </c>
     </row>
     <row r="188">
@@ -7749,22 +7749,22 @@
         <v>26</v>
       </c>
       <c r="E188" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G188" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J188" s="0">
-        <v>1254.9603</v>
+        <v>412.1336</v>
       </c>
     </row>
     <row r="189">
@@ -7784,19 +7784,19 @@
         <v>32</v>
       </c>
       <c r="F189" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H189" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J189" s="0">
-        <v>412.1336</v>
+        <v>395.3304</v>
       </c>
     </row>
     <row r="190">
@@ -7816,19 +7816,19 @@
         <v>32</v>
       </c>
       <c r="F190" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G190" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J190" s="0">
-        <v>395.3304</v>
+        <v>314.40159999999997</v>
       </c>
     </row>
     <row r="191">
@@ -7848,19 +7848,19 @@
         <v>32</v>
       </c>
       <c r="F191" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G191" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J191" s="0">
-        <v>314.40159999999997</v>
+        <v>306.70960000000002</v>
       </c>
     </row>
     <row r="192">
@@ -7880,19 +7880,19 @@
         <v>32</v>
       </c>
       <c r="F192" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G192" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J192" s="0">
-        <v>306.70960000000002</v>
+        <v>285.86070000000001</v>
       </c>
     </row>
     <row r="193">
@@ -7912,19 +7912,19 @@
         <v>32</v>
       </c>
       <c r="F193" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G193" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J193" s="0">
-        <v>285.86070000000001</v>
+        <v>284.4486</v>
       </c>
     </row>
     <row r="194">
@@ -7944,19 +7944,19 @@
         <v>32</v>
       </c>
       <c r="F194" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G194" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J194" s="0">
-        <v>284.4486</v>
+        <v>281.97449999999998</v>
       </c>
     </row>
     <row r="195">
@@ -7970,25 +7970,25 @@
         <v>8</v>
       </c>
       <c r="D195" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F195" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G195" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J195" s="0">
-        <v>281.97449999999998</v>
+        <v>9423.6895000000004</v>
       </c>
     </row>
     <row r="196">
@@ -8008,19 +8008,19 @@
         <v>30</v>
       </c>
       <c r="F196" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G196" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J196" s="0">
-        <v>9423.6895000000004</v>
+        <v>9234.3525000000009</v>
       </c>
     </row>
     <row r="197">
@@ -8037,22 +8037,22 @@
         <v>27</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F197" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G197" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J197" s="0">
-        <v>9234.3525000000009</v>
+        <v>1208.9946</v>
       </c>
     </row>
     <row r="198">
@@ -8072,19 +8072,19 @@
         <v>31</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G198" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J198" s="0">
-        <v>1208.9946</v>
+        <v>951.19749999999999</v>
       </c>
     </row>
     <row r="199">
@@ -8101,22 +8101,22 @@
         <v>27</v>
       </c>
       <c r="E199" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F199" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G199" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J199" s="0">
-        <v>951.19749999999999</v>
+        <v>316.12619999999998</v>
       </c>
     </row>
     <row r="200">
@@ -8136,19 +8136,19 @@
         <v>32</v>
       </c>
       <c r="F200" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G200" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J200" s="0">
-        <v>316.12619999999998</v>
+        <v>302.2124</v>
       </c>
     </row>
     <row r="201">
@@ -8168,19 +8168,19 @@
         <v>32</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G201" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J201" s="0">
-        <v>302.2124</v>
+        <v>294.96859999999998</v>
       </c>
     </row>
     <row r="202">
@@ -8200,19 +8200,19 @@
         <v>32</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G202" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J202" s="0">
-        <v>294.96859999999998</v>
+        <v>291.27109999999999</v>
       </c>
     </row>
     <row r="203">
@@ -8232,19 +8232,19 @@
         <v>32</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G203" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J203" s="0">
-        <v>291.27109999999999</v>
+        <v>264.68939999999998</v>
       </c>
     </row>
     <row r="204">
@@ -8264,19 +8264,19 @@
         <v>32</v>
       </c>
       <c r="F204" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G204" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J204" s="0">
-        <v>264.68939999999998</v>
+        <v>257.6934</v>
       </c>
     </row>
     <row r="205">
@@ -8296,19 +8296,19 @@
         <v>32</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J205" s="0">
-        <v>257.6934</v>
+        <v>214.37610000000001</v>
       </c>
     </row>
     <row r="206">
@@ -8328,19 +8328,19 @@
         <v>32</v>
       </c>
       <c r="F206" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G206" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J206" s="0">
-        <v>214.37610000000001</v>
+        <v>190.58150000000001</v>
       </c>
     </row>
     <row r="207">
@@ -8354,25 +8354,25 @@
         <v>8</v>
       </c>
       <c r="D207" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E207" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F207" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G207" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J207" s="0">
-        <v>190.58150000000001</v>
+        <v>10441.448200000001</v>
       </c>
     </row>
     <row r="208">
@@ -8392,19 +8392,19 @@
         <v>30</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J208" s="0">
-        <v>10441.448200000001</v>
+        <v>9728.8516</v>
       </c>
     </row>
     <row r="209">
@@ -8421,22 +8421,22 @@
         <v>28</v>
       </c>
       <c r="E209" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G209" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J209" s="0">
-        <v>9728.8516</v>
+        <v>1533.4409000000001</v>
       </c>
     </row>
     <row r="210">
@@ -8456,19 +8456,19 @@
         <v>31</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G210" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J210" s="0">
-        <v>1533.4409000000001</v>
+        <v>1358.2428</v>
       </c>
     </row>
     <row r="211">
@@ -8485,22 +8485,22 @@
         <v>28</v>
       </c>
       <c r="E211" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F211" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G211" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J211" s="0">
-        <v>1358.2428</v>
+        <v>452.1069</v>
       </c>
     </row>
     <row r="212">
@@ -8520,19 +8520,19 @@
         <v>32</v>
       </c>
       <c r="F212" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G212" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J212" s="0">
-        <v>452.1069</v>
+        <v>439.75790000000001</v>
       </c>
     </row>
     <row r="213">
@@ -8552,19 +8552,19 @@
         <v>32</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G213" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J213" s="0">
-        <v>439.75790000000001</v>
+        <v>376.52229999999997</v>
       </c>
     </row>
     <row r="214">
@@ -8584,19 +8584,19 @@
         <v>32</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J214" s="0">
-        <v>376.52229999999997</v>
+        <v>375.43979999999999</v>
       </c>
     </row>
     <row r="215">
@@ -8616,19 +8616,19 @@
         <v>32</v>
       </c>
       <c r="F215" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G215" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J215" s="0">
-        <v>375.43979999999999</v>
+        <v>373.55439999999999</v>
       </c>
     </row>
     <row r="216">
@@ -8648,19 +8648,19 @@
         <v>32</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G216" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J216" s="0">
-        <v>373.55439999999999</v>
+        <v>302.76659999999998</v>
       </c>
     </row>
     <row r="217">
@@ -8680,19 +8680,19 @@
         <v>32</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G217" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J217" s="0">
-        <v>302.76659999999998</v>
+        <v>300.86579999999998</v>
       </c>
     </row>
     <row r="218">
@@ -8700,31 +8700,31 @@
         <v>1</v>
       </c>
       <c r="B218" s="0" t="s">
-        <v>3</v>
+        <v>437</v>
       </c>
       <c r="C218" s="0" t="s">
-        <v>8</v>
+        <v>438</v>
       </c>
       <c r="D218" s="0" t="s">
-        <v>28</v>
+        <v>442</v>
       </c>
       <c r="E218" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G218" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>238</v>
+        <v>472</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>434</v>
+        <v>514</v>
       </c>
       <c r="J218" s="0">
-        <v>300.86579999999998</v>
+        <v>12892.7021</v>
       </c>
     </row>
     <row r="219">
@@ -8732,31 +8732,31 @@
         <v>1</v>
       </c>
       <c r="B219" s="0" t="s">
-        <v>3</v>
+        <v>437</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>8</v>
+        <v>438</v>
       </c>
       <c r="D219" s="0" t="s">
-        <v>28</v>
+        <v>442</v>
       </c>
       <c r="E219" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G219" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>239</v>
+        <v>473</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>435</v>
+        <v>515</v>
       </c>
       <c r="J219" s="0">
-        <v>300.18029999999999</v>
+        <v>10694.238300000001</v>
       </c>
     </row>
     <row r="220">
@@ -8773,7 +8773,7 @@
         <v>442</v>
       </c>
       <c r="E220" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F220" s="0" t="s">
         <v>34</v>
@@ -8782,13 +8782,13 @@
         <v>43</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J220" s="0">
-        <v>12892.7021</v>
+        <v>2047.9614999999999</v>
       </c>
     </row>
     <row r="221">
@@ -8805,7 +8805,7 @@
         <v>442</v>
       </c>
       <c r="E221" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F221" s="0" t="s">
         <v>35</v>
@@ -8814,13 +8814,13 @@
         <v>44</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J221" s="0">
-        <v>10694.238300000001</v>
+        <v>910.678</v>
       </c>
     </row>
     <row r="222">
@@ -8837,7 +8837,7 @@
         <v>442</v>
       </c>
       <c r="E222" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F222" s="0" t="s">
         <v>34</v>
@@ -8846,13 +8846,13 @@
         <v>43</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J222" s="0">
-        <v>2047.9614999999999</v>
+        <v>568.2056</v>
       </c>
     </row>
     <row r="223">
@@ -8869,22 +8869,22 @@
         <v>442</v>
       </c>
       <c r="E223" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G223" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="J223" s="0">
-        <v>910.678</v>
+        <v>489.4178</v>
       </c>
     </row>
     <row r="224">
@@ -8904,19 +8904,19 @@
         <v>32</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G224" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="J224" s="0">
-        <v>597.62959999999998</v>
+        <v>370.15899999999999</v>
       </c>
     </row>
     <row r="225">
@@ -8936,19 +8936,19 @@
         <v>32</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H225" s="0" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="J225" s="0">
-        <v>568.2056</v>
+        <v>340.95030000000003</v>
       </c>
     </row>
     <row r="226">

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="29084" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="31110" uniqueCount="559">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="31110" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33136" uniqueCount="559">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33136" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="47264" uniqueCount="559">
   <si>
     <t>Year</t>
   </si>
@@ -4462,13 +4462,13 @@
         <v>43</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="J85" s="0">
-        <v>304.48329999999999</v>
+        <v>297.43759999999998</v>
       </c>
     </row>
     <row r="86">
@@ -4494,13 +4494,13 @@
         <v>44</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="J86" s="0">
-        <v>297.43759999999998</v>
+        <v>283.1619</v>
       </c>
     </row>
     <row r="87">
@@ -4526,13 +4526,13 @@
         <v>44</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="J87" s="0">
-        <v>283.1619</v>
+        <v>247.529</v>
       </c>
     </row>
     <row r="88">
@@ -4558,13 +4558,13 @@
         <v>44</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J88" s="0">
-        <v>247.529</v>
+        <v>231.5712</v>
       </c>
     </row>
     <row r="89">
@@ -4578,25 +4578,25 @@
         <v>438</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J89" s="0">
-        <v>231.5712</v>
+        <v>1517.5046</v>
       </c>
     </row>
     <row r="90">
@@ -4616,19 +4616,19 @@
         <v>31</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J90" s="0">
-        <v>1517.5046</v>
+        <v>1414.645</v>
       </c>
     </row>
     <row r="91">
@@ -4645,22 +4645,22 @@
         <v>527</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="J91" s="0">
-        <v>1414.645</v>
+        <v>385.28089999999998</v>
       </c>
     </row>
     <row r="92">
@@ -4680,19 +4680,19 @@
         <v>32</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G92" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J92" s="0">
-        <v>385.28089999999998</v>
+        <v>310.61110000000002</v>
       </c>
     </row>
     <row r="93">
@@ -4712,19 +4712,19 @@
         <v>32</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G93" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J93" s="0">
-        <v>310.61110000000002</v>
+        <v>277.84199999999999</v>
       </c>
     </row>
     <row r="94">
@@ -4744,19 +4744,19 @@
         <v>32</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G94" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>459</v>
+        <v>63</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J94" s="0">
-        <v>277.84199999999999</v>
+        <v>223.45169999999999</v>
       </c>
     </row>
     <row r="95">
@@ -4770,25 +4770,25 @@
         <v>438</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G95" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>63</v>
+        <v>460</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J95" s="0">
-        <v>223.45169999999999</v>
+        <v>10215.762699999999</v>
       </c>
     </row>
     <row r="96">
@@ -4808,19 +4808,19 @@
         <v>30</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J96" s="0">
-        <v>10215.762699999999</v>
+        <v>8851.0136999999995</v>
       </c>
     </row>
     <row r="97">
@@ -4837,22 +4837,22 @@
         <v>528</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="J97" s="0">
-        <v>8851.0136999999995</v>
+        <v>1106.4232</v>
       </c>
     </row>
     <row r="98">
@@ -4872,19 +4872,19 @@
         <v>31</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J98" s="0">
-        <v>1106.4232</v>
+        <v>909.94200000000001</v>
       </c>
     </row>
     <row r="99">
@@ -4901,22 +4901,22 @@
         <v>528</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J99" s="0">
-        <v>909.94200000000001</v>
+        <v>316.77910000000003</v>
       </c>
     </row>
     <row r="100">
@@ -4936,19 +4936,19 @@
         <v>32</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G100" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J100" s="0">
-        <v>316.77910000000003</v>
+        <v>284.43700000000001</v>
       </c>
     </row>
     <row r="101">
@@ -4968,19 +4968,19 @@
         <v>32</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G101" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="J101" s="0">
-        <v>284.43700000000001</v>
+        <v>282.07659999999999</v>
       </c>
     </row>
     <row r="102">
@@ -5000,19 +5000,19 @@
         <v>32</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G102" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J102" s="0">
-        <v>282.07659999999999</v>
+        <v>261.52760000000001</v>
       </c>
     </row>
     <row r="103">
@@ -5032,19 +5032,19 @@
         <v>32</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J103" s="0">
-        <v>261.52760000000001</v>
+        <v>248.01570000000001</v>
       </c>
     </row>
     <row r="104">
@@ -5064,19 +5064,19 @@
         <v>32</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G104" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J104" s="0">
-        <v>248.01570000000001</v>
+        <v>246.53380000000001</v>
       </c>
     </row>
     <row r="105">
@@ -5096,19 +5096,19 @@
         <v>32</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="J105" s="0">
-        <v>246.53380000000001</v>
+        <v>228.9768</v>
       </c>
     </row>
     <row r="106">
@@ -5128,19 +5128,19 @@
         <v>32</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G106" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="J106" s="0">
-        <v>228.9768</v>
+        <v>216.21680000000001</v>
       </c>
     </row>
     <row r="107">
@@ -5151,28 +5151,28 @@
         <v>3</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>438</v>
+        <v>7</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>528</v>
+        <v>19</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>471</v>
+        <v>123</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>558</v>
+        <v>319</v>
       </c>
       <c r="J107" s="0">
-        <v>216.21680000000001</v>
+        <v>10261.8174</v>
       </c>
     </row>
     <row r="108">
@@ -5192,19 +5192,19 @@
         <v>30</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J108" s="0">
-        <v>10261.8174</v>
+        <v>9826.5293000000001</v>
       </c>
     </row>
     <row r="109">
@@ -5221,22 +5221,22 @@
         <v>19</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J109" s="0">
-        <v>9826.5293000000001</v>
+        <v>310.85700000000003</v>
       </c>
     </row>
     <row r="110">
@@ -5256,19 +5256,19 @@
         <v>32</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G110" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J110" s="0">
-        <v>310.85700000000003</v>
+        <v>294.82119999999998</v>
       </c>
     </row>
     <row r="111">
@@ -5288,19 +5288,19 @@
         <v>32</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G111" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J111" s="0">
-        <v>294.82119999999998</v>
+        <v>290.76960000000003</v>
       </c>
     </row>
     <row r="112">
@@ -5320,19 +5320,19 @@
         <v>32</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G112" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J112" s="0">
-        <v>290.76960000000003</v>
+        <v>273.49590000000001</v>
       </c>
     </row>
     <row r="113">
@@ -5352,19 +5352,19 @@
         <v>32</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J113" s="0">
-        <v>273.49590000000001</v>
+        <v>242.22909999999999</v>
       </c>
     </row>
     <row r="114">
@@ -5384,19 +5384,19 @@
         <v>32</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J114" s="0">
-        <v>242.22909999999999</v>
+        <v>238.70050000000001</v>
       </c>
     </row>
     <row r="115">
@@ -5416,19 +5416,19 @@
         <v>32</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J115" s="0">
-        <v>238.70050000000001</v>
+        <v>227.2551</v>
       </c>
     </row>
     <row r="116">
@@ -5448,19 +5448,19 @@
         <v>32</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G116" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J116" s="0">
-        <v>227.2551</v>
+        <v>214.56540000000001</v>
       </c>
     </row>
     <row r="117">
@@ -5474,25 +5474,25 @@
         <v>7</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J117" s="0">
-        <v>214.56540000000001</v>
+        <v>9905.6357000000007</v>
       </c>
     </row>
     <row r="118">
@@ -5512,19 +5512,19 @@
         <v>30</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J118" s="0">
-        <v>9905.6357000000007</v>
+        <v>8499.6309000000001</v>
       </c>
     </row>
     <row r="119">
@@ -5541,22 +5541,22 @@
         <v>20</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J119" s="0">
-        <v>8499.6309000000001</v>
+        <v>1404.5636</v>
       </c>
     </row>
     <row r="120">
@@ -5573,7 +5573,7 @@
         <v>20</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F120" s="0" t="s">
         <v>34</v>
@@ -5582,13 +5582,13 @@
         <v>43</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J120" s="0">
-        <v>1404.5636</v>
+        <v>315.27960000000002</v>
       </c>
     </row>
     <row r="121">
@@ -5608,19 +5608,19 @@
         <v>32</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G121" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J121" s="0">
-        <v>315.27960000000002</v>
+        <v>302.22129999999999</v>
       </c>
     </row>
     <row r="122">
@@ -5640,19 +5640,19 @@
         <v>32</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G122" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J122" s="0">
-        <v>302.22129999999999</v>
+        <v>266.9862</v>
       </c>
     </row>
     <row r="123">
@@ -5672,19 +5672,19 @@
         <v>32</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J123" s="0">
-        <v>266.9862</v>
+        <v>264.11059999999998</v>
       </c>
     </row>
     <row r="124">
@@ -5704,19 +5704,19 @@
         <v>32</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J124" s="0">
-        <v>264.11059999999998</v>
+        <v>247.79859999999999</v>
       </c>
     </row>
     <row r="125">
@@ -5736,19 +5736,19 @@
         <v>32</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J125" s="0">
-        <v>247.79859999999999</v>
+        <v>239.36019999999999</v>
       </c>
     </row>
     <row r="126">
@@ -5768,19 +5768,19 @@
         <v>32</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G126" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J126" s="0">
-        <v>239.36019999999999</v>
+        <v>208.72989999999999</v>
       </c>
     </row>
     <row r="127">
@@ -5800,19 +5800,19 @@
         <v>32</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G127" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J127" s="0">
-        <v>208.72989999999999</v>
+        <v>199.44909999999999</v>
       </c>
     </row>
     <row r="128">
@@ -5826,25 +5826,25 @@
         <v>7</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J128" s="0">
-        <v>199.44909999999999</v>
+        <v>9596.9883000000009</v>
       </c>
     </row>
     <row r="129">
@@ -5864,19 +5864,19 @@
         <v>30</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J129" s="0">
-        <v>9596.9883000000009</v>
+        <v>8798.1787000000004</v>
       </c>
     </row>
     <row r="130">
@@ -5893,22 +5893,22 @@
         <v>21</v>
       </c>
       <c r="E130" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G130" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J130" s="0">
-        <v>8798.1787000000004</v>
+        <v>1321.1365000000001</v>
       </c>
     </row>
     <row r="131">
@@ -5928,19 +5928,19 @@
         <v>31</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J131" s="0">
-        <v>1321.1365000000001</v>
+        <v>959.9144</v>
       </c>
     </row>
     <row r="132">
@@ -5957,22 +5957,22 @@
         <v>21</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J132" s="0">
-        <v>959.9144</v>
+        <v>309.23169999999999</v>
       </c>
     </row>
     <row r="133">
@@ -5992,19 +5992,19 @@
         <v>32</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J133" s="0">
-        <v>309.23169999999999</v>
+        <v>301.12470000000002</v>
       </c>
     </row>
     <row r="134">
@@ -6024,19 +6024,19 @@
         <v>32</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J134" s="0">
-        <v>301.12470000000002</v>
+        <v>296.84010000000001</v>
       </c>
     </row>
     <row r="135">
@@ -6056,19 +6056,19 @@
         <v>32</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J135" s="0">
-        <v>296.84010000000001</v>
+        <v>288.2115</v>
       </c>
     </row>
     <row r="136">
@@ -6088,19 +6088,19 @@
         <v>32</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J136" s="0">
-        <v>288.2115</v>
+        <v>274.3639</v>
       </c>
     </row>
     <row r="137">
@@ -6120,19 +6120,19 @@
         <v>32</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G137" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J137" s="0">
-        <v>274.3639</v>
+        <v>260.00229999999999</v>
       </c>
     </row>
     <row r="138">
@@ -6152,19 +6152,19 @@
         <v>32</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G138" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J138" s="0">
-        <v>260.00229999999999</v>
+        <v>246.21190000000001</v>
       </c>
     </row>
     <row r="139">
@@ -6184,19 +6184,19 @@
         <v>32</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J139" s="0">
-        <v>246.21190000000001</v>
+        <v>180.47190000000001</v>
       </c>
     </row>
     <row r="140">
@@ -6210,25 +6210,25 @@
         <v>7</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J140" s="0">
-        <v>180.47190000000001</v>
+        <v>9836.6807000000008</v>
       </c>
     </row>
     <row r="141">
@@ -6245,7 +6245,7 @@
         <v>22</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F141" s="0" t="s">
         <v>34</v>
@@ -6254,13 +6254,13 @@
         <v>43</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J141" s="0">
-        <v>9836.6807000000008</v>
+        <v>908.87840000000006</v>
       </c>
     </row>
     <row r="142">
@@ -6280,19 +6280,19 @@
         <v>31</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G142" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J142" s="0">
-        <v>908.87840000000006</v>
+        <v>840.46699999999999</v>
       </c>
     </row>
     <row r="143">
@@ -6309,22 +6309,22 @@
         <v>22</v>
       </c>
       <c r="E143" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J143" s="0">
-        <v>840.46699999999999</v>
+        <v>385.22919999999999</v>
       </c>
     </row>
     <row r="144">
@@ -6344,19 +6344,19 @@
         <v>32</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G144" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J144" s="0">
-        <v>385.22919999999999</v>
+        <v>310.47890000000001</v>
       </c>
     </row>
     <row r="145">
@@ -6376,19 +6376,19 @@
         <v>32</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J145" s="0">
-        <v>310.47890000000001</v>
+        <v>300.91699999999997</v>
       </c>
     </row>
     <row r="146">
@@ -6408,19 +6408,19 @@
         <v>32</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G146" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J146" s="0">
-        <v>300.91699999999997</v>
+        <v>285.7113</v>
       </c>
     </row>
     <row r="147">
@@ -6440,19 +6440,19 @@
         <v>32</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G147" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J147" s="0">
-        <v>285.7113</v>
+        <v>255.1182</v>
       </c>
     </row>
     <row r="148">
@@ -6472,19 +6472,19 @@
         <v>32</v>
       </c>
       <c r="F148" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G148" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J148" s="0">
-        <v>255.1182</v>
+        <v>251.63229999999999</v>
       </c>
     </row>
     <row r="149">
@@ -6504,19 +6504,19 @@
         <v>32</v>
       </c>
       <c r="F149" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G149" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J149" s="0">
-        <v>251.63229999999999</v>
+        <v>241.47989999999999</v>
       </c>
     </row>
     <row r="150">
@@ -6536,19 +6536,19 @@
         <v>32</v>
       </c>
       <c r="F150" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G150" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J150" s="0">
-        <v>241.47989999999999</v>
+        <v>239.88820000000001</v>
       </c>
     </row>
     <row r="151">
@@ -6559,28 +6559,28 @@
         <v>3</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E151" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F151" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J151" s="0">
-        <v>239.88820000000001</v>
+        <v>10661.891600000001</v>
       </c>
     </row>
     <row r="152">
@@ -6600,19 +6600,19 @@
         <v>30</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G152" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J152" s="0">
-        <v>10661.891600000001</v>
+        <v>7643.7520000000004</v>
       </c>
     </row>
     <row r="153">
@@ -6629,22 +6629,22 @@
         <v>23</v>
       </c>
       <c r="E153" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F153" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G153" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H153" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J153" s="0">
-        <v>7643.7520000000004</v>
+        <v>1539.2754</v>
       </c>
     </row>
     <row r="154">
@@ -6664,19 +6664,19 @@
         <v>31</v>
       </c>
       <c r="F154" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G154" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J154" s="0">
-        <v>1539.2754</v>
+        <v>1393.9193</v>
       </c>
     </row>
     <row r="155">
@@ -6693,22 +6693,22 @@
         <v>23</v>
       </c>
       <c r="E155" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F155" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G155" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J155" s="0">
-        <v>1393.9193</v>
+        <v>457.66739999999999</v>
       </c>
     </row>
     <row r="156">
@@ -6728,19 +6728,19 @@
         <v>32</v>
       </c>
       <c r="F156" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G156" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J156" s="0">
-        <v>457.66739999999999</v>
+        <v>419.16669999999999</v>
       </c>
     </row>
     <row r="157">
@@ -6760,19 +6760,19 @@
         <v>32</v>
       </c>
       <c r="F157" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G157" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H157" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J157" s="0">
-        <v>419.16669999999999</v>
+        <v>417.49169999999998</v>
       </c>
     </row>
     <row r="158">
@@ -6792,19 +6792,19 @@
         <v>32</v>
       </c>
       <c r="F158" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G158" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H158" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J158" s="0">
-        <v>417.49169999999998</v>
+        <v>399.00799999999998</v>
       </c>
     </row>
     <row r="159">
@@ -6824,19 +6824,19 @@
         <v>32</v>
       </c>
       <c r="F159" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G159" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H159" s="0" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J159" s="0">
-        <v>399.00799999999998</v>
+        <v>361.1662</v>
       </c>
     </row>
     <row r="160">
@@ -6856,19 +6856,19 @@
         <v>32</v>
       </c>
       <c r="F160" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G160" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H160" s="0" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J160" s="0">
-        <v>361.1662</v>
+        <v>311.19600000000003</v>
       </c>
     </row>
     <row r="161">
@@ -6888,19 +6888,19 @@
         <v>32</v>
       </c>
       <c r="F161" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G161" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H161" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J161" s="0">
-        <v>311.19600000000003</v>
+        <v>291.23480000000001</v>
       </c>
     </row>
     <row r="162">
@@ -6914,25 +6914,25 @@
         <v>8</v>
       </c>
       <c r="D162" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E162" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F162" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G162" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H162" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J162" s="0">
-        <v>291.23480000000001</v>
+        <v>9127.5985999999994</v>
       </c>
     </row>
     <row r="163">
@@ -6952,19 +6952,19 @@
         <v>30</v>
       </c>
       <c r="F163" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G163" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H163" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J163" s="0">
-        <v>9127.5985999999994</v>
+        <v>8554.8642999999993</v>
       </c>
     </row>
     <row r="164">
@@ -6981,22 +6981,22 @@
         <v>24</v>
       </c>
       <c r="E164" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F164" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G164" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H164" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J164" s="0">
-        <v>8554.8642999999993</v>
+        <v>1414.848</v>
       </c>
     </row>
     <row r="165">
@@ -7016,19 +7016,19 @@
         <v>31</v>
       </c>
       <c r="F165" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G165" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H165" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J165" s="0">
-        <v>1414.848</v>
+        <v>752.67660000000001</v>
       </c>
     </row>
     <row r="166">
@@ -7045,22 +7045,22 @@
         <v>24</v>
       </c>
       <c r="E166" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F166" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G166" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J166" s="0">
-        <v>752.67660000000001</v>
+        <v>348.73090000000002</v>
       </c>
     </row>
     <row r="167">
@@ -7080,19 +7080,19 @@
         <v>32</v>
       </c>
       <c r="F167" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G167" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J167" s="0">
-        <v>348.73090000000002</v>
+        <v>307.04939999999999</v>
       </c>
     </row>
     <row r="168">
@@ -7112,19 +7112,19 @@
         <v>32</v>
       </c>
       <c r="F168" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G168" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J168" s="0">
-        <v>307.04939999999999</v>
+        <v>280.97919999999999</v>
       </c>
     </row>
     <row r="169">
@@ -7144,19 +7144,19 @@
         <v>32</v>
       </c>
       <c r="F169" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G169" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H169" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J169" s="0">
-        <v>280.97919999999999</v>
+        <v>265.1284</v>
       </c>
     </row>
     <row r="170">
@@ -7176,19 +7176,19 @@
         <v>32</v>
       </c>
       <c r="F170" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G170" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H170" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J170" s="0">
-        <v>265.1284</v>
+        <v>249.8895</v>
       </c>
     </row>
     <row r="171">
@@ -7208,19 +7208,19 @@
         <v>32</v>
       </c>
       <c r="F171" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G171" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H171" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J171" s="0">
-        <v>249.8895</v>
+        <v>215.3955</v>
       </c>
     </row>
     <row r="172">
@@ -7240,19 +7240,19 @@
         <v>32</v>
       </c>
       <c r="F172" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G172" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H172" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J172" s="0">
-        <v>215.3955</v>
+        <v>213.6302</v>
       </c>
     </row>
     <row r="173">
@@ -7272,19 +7272,19 @@
         <v>32</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G173" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J173" s="0">
-        <v>213.6302</v>
+        <v>193.54920000000001</v>
       </c>
     </row>
     <row r="174">
@@ -7298,25 +7298,25 @@
         <v>8</v>
       </c>
       <c r="D174" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E174" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F174" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G174" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J174" s="0">
-        <v>193.54920000000001</v>
+        <v>9254.9814000000006</v>
       </c>
     </row>
     <row r="175">
@@ -7336,19 +7336,19 @@
         <v>30</v>
       </c>
       <c r="F175" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G175" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J175" s="0">
-        <v>9254.9814000000006</v>
+        <v>8396.3974999999991</v>
       </c>
     </row>
     <row r="176">
@@ -7365,22 +7365,22 @@
         <v>25</v>
       </c>
       <c r="E176" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G176" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J176" s="0">
-        <v>8396.3974999999991</v>
+        <v>1087.1931999999999</v>
       </c>
     </row>
     <row r="177">
@@ -7400,19 +7400,19 @@
         <v>31</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G177" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J177" s="0">
-        <v>1087.1931999999999</v>
+        <v>1026.0048999999999</v>
       </c>
     </row>
     <row r="178">
@@ -7429,22 +7429,22 @@
         <v>25</v>
       </c>
       <c r="E178" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F178" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G178" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J178" s="0">
-        <v>1026.0048999999999</v>
+        <v>328.2697</v>
       </c>
     </row>
     <row r="179">
@@ -7464,19 +7464,19 @@
         <v>32</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G179" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J179" s="0">
-        <v>328.2697</v>
+        <v>306.13749999999999</v>
       </c>
     </row>
     <row r="180">
@@ -7496,19 +7496,19 @@
         <v>32</v>
       </c>
       <c r="F180" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G180" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J180" s="0">
-        <v>306.13749999999999</v>
+        <v>302.69369999999998</v>
       </c>
     </row>
     <row r="181">
@@ -7528,19 +7528,19 @@
         <v>32</v>
       </c>
       <c r="F181" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G181" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J181" s="0">
-        <v>302.69369999999998</v>
+        <v>296.63529999999997</v>
       </c>
     </row>
     <row r="182">
@@ -7560,19 +7560,19 @@
         <v>32</v>
       </c>
       <c r="F182" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G182" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H182" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J182" s="0">
-        <v>296.63529999999997</v>
+        <v>292.96969999999999</v>
       </c>
     </row>
     <row r="183">
@@ -7592,19 +7592,19 @@
         <v>32</v>
       </c>
       <c r="F183" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G183" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J183" s="0">
-        <v>292.96969999999999</v>
+        <v>267.35629999999998</v>
       </c>
     </row>
     <row r="184">
@@ -7624,19 +7624,19 @@
         <v>32</v>
       </c>
       <c r="F184" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G184" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J184" s="0">
-        <v>267.35629999999998</v>
+        <v>165.21969999999999</v>
       </c>
     </row>
     <row r="185">
@@ -7650,25 +7650,25 @@
         <v>8</v>
       </c>
       <c r="D185" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F185" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G185" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="J185" s="0">
-        <v>165.21969999999999</v>
+        <v>1713.3430000000001</v>
       </c>
     </row>
     <row r="186">
@@ -7688,19 +7688,19 @@
         <v>31</v>
       </c>
       <c r="F186" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G186" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H186" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J186" s="0">
-        <v>1713.3430000000001</v>
+        <v>1254.9603</v>
       </c>
     </row>
     <row r="187">
@@ -7717,22 +7717,22 @@
         <v>26</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G187" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H187" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J187" s="0">
-        <v>1254.9603</v>
+        <v>412.1336</v>
       </c>
     </row>
     <row r="188">
@@ -7752,19 +7752,19 @@
         <v>32</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J188" s="0">
-        <v>412.1336</v>
+        <v>395.3304</v>
       </c>
     </row>
     <row r="189">
@@ -7784,19 +7784,19 @@
         <v>32</v>
       </c>
       <c r="F189" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H189" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J189" s="0">
-        <v>395.3304</v>
+        <v>314.40159999999997</v>
       </c>
     </row>
     <row r="190">
@@ -7816,19 +7816,19 @@
         <v>32</v>
       </c>
       <c r="F190" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G190" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J190" s="0">
-        <v>314.40159999999997</v>
+        <v>306.70960000000002</v>
       </c>
     </row>
     <row r="191">
@@ -7848,19 +7848,19 @@
         <v>32</v>
       </c>
       <c r="F191" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G191" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J191" s="0">
-        <v>306.70960000000002</v>
+        <v>285.86070000000001</v>
       </c>
     </row>
     <row r="192">
@@ -7880,19 +7880,19 @@
         <v>32</v>
       </c>
       <c r="F192" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G192" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J192" s="0">
-        <v>285.86070000000001</v>
+        <v>284.4486</v>
       </c>
     </row>
     <row r="193">
@@ -7912,19 +7912,19 @@
         <v>32</v>
       </c>
       <c r="F193" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G193" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J193" s="0">
-        <v>284.4486</v>
+        <v>281.97449999999998</v>
       </c>
     </row>
     <row r="194">
@@ -7938,25 +7938,25 @@
         <v>8</v>
       </c>
       <c r="D194" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E194" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F194" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G194" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J194" s="0">
-        <v>281.97449999999998</v>
+        <v>9423.6895000000004</v>
       </c>
     </row>
     <row r="195">
@@ -7976,19 +7976,19 @@
         <v>30</v>
       </c>
       <c r="F195" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G195" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J195" s="0">
-        <v>9423.6895000000004</v>
+        <v>9234.3525000000009</v>
       </c>
     </row>
     <row r="196">
@@ -8005,22 +8005,22 @@
         <v>27</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F196" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G196" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J196" s="0">
-        <v>9234.3525000000009</v>
+        <v>1208.9946</v>
       </c>
     </row>
     <row r="197">
@@ -8040,19 +8040,19 @@
         <v>31</v>
       </c>
       <c r="F197" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G197" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J197" s="0">
-        <v>1208.9946</v>
+        <v>951.19749999999999</v>
       </c>
     </row>
     <row r="198">
@@ -8069,22 +8069,22 @@
         <v>27</v>
       </c>
       <c r="E198" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G198" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J198" s="0">
-        <v>951.19749999999999</v>
+        <v>316.12619999999998</v>
       </c>
     </row>
     <row r="199">
@@ -8104,19 +8104,19 @@
         <v>32</v>
       </c>
       <c r="F199" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G199" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J199" s="0">
-        <v>316.12619999999998</v>
+        <v>302.2124</v>
       </c>
     </row>
     <row r="200">
@@ -8136,19 +8136,19 @@
         <v>32</v>
       </c>
       <c r="F200" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G200" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J200" s="0">
-        <v>302.2124</v>
+        <v>294.96859999999998</v>
       </c>
     </row>
     <row r="201">
@@ -8168,19 +8168,19 @@
         <v>32</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G201" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J201" s="0">
-        <v>294.96859999999998</v>
+        <v>291.27109999999999</v>
       </c>
     </row>
     <row r="202">
@@ -8200,19 +8200,19 @@
         <v>32</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G202" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J202" s="0">
-        <v>291.27109999999999</v>
+        <v>264.68939999999998</v>
       </c>
     </row>
     <row r="203">
@@ -8232,19 +8232,19 @@
         <v>32</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J203" s="0">
-        <v>264.68939999999998</v>
+        <v>257.6934</v>
       </c>
     </row>
     <row r="204">
@@ -8264,19 +8264,19 @@
         <v>32</v>
       </c>
       <c r="F204" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G204" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J204" s="0">
-        <v>257.6934</v>
+        <v>214.37610000000001</v>
       </c>
     </row>
     <row r="205">
@@ -8296,19 +8296,19 @@
         <v>32</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J205" s="0">
-        <v>214.37610000000001</v>
+        <v>190.58150000000001</v>
       </c>
     </row>
     <row r="206">
@@ -8322,25 +8322,25 @@
         <v>8</v>
       </c>
       <c r="D206" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F206" s="0" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G206" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J206" s="0">
-        <v>190.58150000000001</v>
+        <v>10441.448200000001</v>
       </c>
     </row>
     <row r="207">
@@ -8360,19 +8360,19 @@
         <v>30</v>
       </c>
       <c r="F207" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G207" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J207" s="0">
-        <v>10441.448200000001</v>
+        <v>9728.8516</v>
       </c>
     </row>
     <row r="208">
@@ -8389,22 +8389,22 @@
         <v>28</v>
       </c>
       <c r="E208" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J208" s="0">
-        <v>9728.8516</v>
+        <v>1533.4409000000001</v>
       </c>
     </row>
     <row r="209">
@@ -8424,19 +8424,19 @@
         <v>31</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G209" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J209" s="0">
-        <v>1533.4409000000001</v>
+        <v>1358.2428</v>
       </c>
     </row>
     <row r="210">
@@ -8453,22 +8453,22 @@
         <v>28</v>
       </c>
       <c r="E210" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G210" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J210" s="0">
-        <v>1358.2428</v>
+        <v>452.1069</v>
       </c>
     </row>
     <row r="211">
@@ -8488,19 +8488,19 @@
         <v>32</v>
       </c>
       <c r="F211" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G211" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J211" s="0">
-        <v>452.1069</v>
+        <v>439.75790000000001</v>
       </c>
     </row>
     <row r="212">
@@ -8520,19 +8520,19 @@
         <v>32</v>
       </c>
       <c r="F212" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G212" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J212" s="0">
-        <v>439.75790000000001</v>
+        <v>376.52229999999997</v>
       </c>
     </row>
     <row r="213">
@@ -8552,19 +8552,19 @@
         <v>32</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G213" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J213" s="0">
-        <v>376.52229999999997</v>
+        <v>375.43979999999999</v>
       </c>
     </row>
     <row r="214">
@@ -8584,19 +8584,19 @@
         <v>32</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G214" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J214" s="0">
-        <v>375.43979999999999</v>
+        <v>373.55439999999999</v>
       </c>
     </row>
     <row r="215">
@@ -8616,19 +8616,19 @@
         <v>32</v>
       </c>
       <c r="F215" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G215" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J215" s="0">
-        <v>373.55439999999999</v>
+        <v>302.76659999999998</v>
       </c>
     </row>
     <row r="216">
@@ -8648,19 +8648,19 @@
         <v>32</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G216" s="0" t="s">
         <v>44</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J216" s="0">
-        <v>302.76659999999998</v>
+        <v>300.86579999999998</v>
       </c>
     </row>
     <row r="217">
@@ -8668,31 +8668,31 @@
         <v>1</v>
       </c>
       <c r="B217" s="0" t="s">
-        <v>3</v>
+        <v>437</v>
       </c>
       <c r="C217" s="0" t="s">
-        <v>8</v>
+        <v>438</v>
       </c>
       <c r="D217" s="0" t="s">
-        <v>28</v>
+        <v>442</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G217" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>238</v>
+        <v>472</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>434</v>
+        <v>514</v>
       </c>
       <c r="J217" s="0">
-        <v>300.86579999999998</v>
+        <v>12892.7021</v>
       </c>
     </row>
     <row r="218">
@@ -8712,19 +8712,19 @@
         <v>30</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G218" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J218" s="0">
-        <v>12892.7021</v>
+        <v>10694.238300000001</v>
       </c>
     </row>
     <row r="219">
@@ -8741,22 +8741,22 @@
         <v>442</v>
       </c>
       <c r="E219" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G219" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J219" s="0">
-        <v>10694.238300000001</v>
+        <v>2047.9614999999999</v>
       </c>
     </row>
     <row r="220">
@@ -8776,19 +8776,19 @@
         <v>31</v>
       </c>
       <c r="F220" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G220" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J220" s="0">
-        <v>2047.9614999999999</v>
+        <v>910.678</v>
       </c>
     </row>
     <row r="221">
@@ -8805,22 +8805,22 @@
         <v>442</v>
       </c>
       <c r="E221" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G221" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="J221" s="0">
-        <v>910.678</v>
+        <v>568.2056</v>
       </c>
     </row>
     <row r="222">
@@ -8840,19 +8840,19 @@
         <v>32</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G222" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J222" s="0">
-        <v>568.2056</v>
+        <v>489.4178</v>
       </c>
     </row>
     <row r="223">
@@ -8872,19 +8872,19 @@
         <v>32</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G223" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J223" s="0">
-        <v>489.4178</v>
+        <v>370.15899999999999</v>
       </c>
     </row>
     <row r="224">
@@ -8904,19 +8904,19 @@
         <v>32</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G224" s="0" t="s">
         <v>43</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="J224" s="0">
-        <v>370.15899999999999</v>
+        <v>340.95030000000003</v>
       </c>
     </row>
     <row r="225">

--- a/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2023_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="47264" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49281" uniqueCount="559">
   <si>
     <t>Year</t>
   </si>
